--- a/AAII_Financials/Yearly/WF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WF_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>WF</t>
   </si>
@@ -656,111 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>11284000</v>
+        <v>15687600</v>
       </c>
       <c r="E8" s="3">
-        <v>7619000</v>
+        <v>11137500</v>
       </c>
       <c r="F8" s="3">
-        <v>7333400</v>
+        <v>7520000</v>
       </c>
       <c r="G8" s="3">
-        <v>8144100</v>
+        <v>7238100</v>
       </c>
       <c r="H8" s="3">
-        <v>7457100</v>
+        <v>8038300</v>
       </c>
       <c r="I8" s="3">
-        <v>6584000</v>
+        <v>7360200</v>
       </c>
       <c r="J8" s="3">
+        <v>6498500</v>
+      </c>
+      <c r="K8" s="3">
         <v>6554500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6436700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7461100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8639000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9148600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9763900</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -800,9 +806,12 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -842,9 +851,12 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,9 +960,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -986,51 +1005,57 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-404800</v>
+        <v>-386400</v>
       </c>
       <c r="E15" s="3">
-        <v>-405800</v>
+        <v>-399600</v>
       </c>
       <c r="F15" s="3">
-        <v>-403200</v>
+        <v>-400500</v>
       </c>
       <c r="G15" s="3">
-        <v>-372200</v>
+        <v>-398000</v>
       </c>
       <c r="H15" s="3">
-        <v>-170000</v>
+        <v>-367400</v>
       </c>
       <c r="I15" s="3">
-        <v>-144400</v>
+        <v>-167800</v>
       </c>
       <c r="J15" s="3">
+        <v>-142500</v>
+      </c>
+      <c r="K15" s="3">
         <v>-194100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-178200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-184600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-215000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-187500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-177900</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5269300</v>
+        <v>10483400</v>
       </c>
       <c r="E17" s="3">
-        <v>2669200</v>
+        <v>5200900</v>
       </c>
       <c r="F17" s="3">
-        <v>3325000</v>
+        <v>2634600</v>
       </c>
       <c r="G17" s="3">
-        <v>3894100</v>
+        <v>3281800</v>
       </c>
       <c r="H17" s="3">
-        <v>3428500</v>
+        <v>3843600</v>
       </c>
       <c r="I17" s="3">
-        <v>3228100</v>
+        <v>3384000</v>
       </c>
       <c r="J17" s="3">
+        <v>3186200</v>
+      </c>
+      <c r="K17" s="3">
         <v>3375300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3735900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4725900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6553500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6595600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7124100</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>6014700</v>
+        <v>5204200</v>
       </c>
       <c r="E18" s="3">
-        <v>4949700</v>
+        <v>5936600</v>
       </c>
       <c r="F18" s="3">
-        <v>4008400</v>
+        <v>4885400</v>
       </c>
       <c r="G18" s="3">
-        <v>4250000</v>
+        <v>3956300</v>
       </c>
       <c r="H18" s="3">
-        <v>4028600</v>
+        <v>4194800</v>
       </c>
       <c r="I18" s="3">
-        <v>3356000</v>
+        <v>3976300</v>
       </c>
       <c r="J18" s="3">
+        <v>3312400</v>
+      </c>
+      <c r="K18" s="3">
         <v>3179200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2700800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2735200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2085400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2553000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2639700</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,92 +1178,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2561000</v>
+        <v>-2530900</v>
       </c>
       <c r="E20" s="3">
-        <v>-2062800</v>
+        <v>-2527700</v>
       </c>
       <c r="F20" s="3">
-        <v>-2467400</v>
+        <v>-2036000</v>
       </c>
       <c r="G20" s="3">
-        <v>-2153200</v>
+        <v>-2435400</v>
       </c>
       <c r="H20" s="3">
-        <v>-1868800</v>
+        <v>-2125300</v>
       </c>
       <c r="I20" s="3">
-        <v>-1854800</v>
+        <v>-1844600</v>
       </c>
       <c r="J20" s="3">
+        <v>-1830700</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1983100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1626400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2059400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1823700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1177200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-578900</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4169300</v>
+        <v>3428100</v>
       </c>
       <c r="E21" s="3">
-        <v>3496700</v>
+        <v>4115200</v>
       </c>
       <c r="F21" s="3">
-        <v>1953300</v>
+        <v>3451300</v>
       </c>
       <c r="G21" s="3">
-        <v>2486200</v>
+        <v>1928000</v>
       </c>
       <c r="H21" s="3">
-        <v>2369600</v>
+        <v>2453900</v>
       </c>
       <c r="I21" s="3">
-        <v>1682700</v>
+        <v>2338800</v>
       </c>
       <c r="J21" s="3">
+        <v>1660800</v>
+      </c>
+      <c r="K21" s="3">
         <v>1390200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1250200</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3">
         <v>532200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1623200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2301600</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1271,93 +1310,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3453700</v>
+        <v>2673300</v>
       </c>
       <c r="E23" s="3">
-        <v>2886900</v>
+        <v>3408900</v>
       </c>
       <c r="F23" s="3">
-        <v>1541000</v>
+        <v>2849400</v>
       </c>
       <c r="G23" s="3">
-        <v>2096700</v>
+        <v>1521000</v>
       </c>
       <c r="H23" s="3">
-        <v>2159800</v>
+        <v>2069500</v>
       </c>
       <c r="I23" s="3">
-        <v>1501100</v>
+        <v>2131700</v>
       </c>
       <c r="J23" s="3">
+        <v>1481600</v>
+      </c>
+      <c r="K23" s="3">
         <v>1196100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1074400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>675900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>261800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1375900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2060800</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>894300</v>
+        <v>676800</v>
       </c>
       <c r="E24" s="3">
-        <v>725200</v>
+        <v>882700</v>
       </c>
       <c r="F24" s="3">
-        <v>374200</v>
+        <v>715800</v>
       </c>
       <c r="G24" s="3">
-        <v>527800</v>
+        <v>369400</v>
       </c>
       <c r="H24" s="3">
-        <v>580000</v>
+        <v>520900</v>
       </c>
       <c r="I24" s="3">
-        <v>323000</v>
+        <v>572400</v>
       </c>
       <c r="J24" s="3">
+        <v>318800</v>
+      </c>
+      <c r="K24" s="3">
         <v>212400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>278600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>233400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>31900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>299700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>491900</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2559500</v>
+        <v>1996400</v>
       </c>
       <c r="E26" s="3">
-        <v>2161700</v>
+        <v>2526200</v>
       </c>
       <c r="F26" s="3">
-        <v>1166700</v>
+        <v>2133600</v>
       </c>
       <c r="G26" s="3">
+        <v>1151600</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1548600</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1559300</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1162900</v>
+      </c>
+      <c r="K26" s="3">
+        <v>983700</v>
+      </c>
+      <c r="L26" s="3">
+        <v>795800</v>
+      </c>
+      <c r="M26" s="3">
+        <v>442400</v>
+      </c>
+      <c r="N26" s="3">
+        <v>229800</v>
+      </c>
+      <c r="O26" s="3">
+        <v>1076100</v>
+      </c>
+      <c r="P26" s="3">
         <v>1568900</v>
       </c>
-      <c r="H26" s="3">
-        <v>1579800</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1178200</v>
-      </c>
-      <c r="J26" s="3">
-        <v>983700</v>
-      </c>
-      <c r="K26" s="3">
-        <v>795800</v>
-      </c>
-      <c r="L26" s="3">
-        <v>442400</v>
-      </c>
-      <c r="M26" s="3">
-        <v>229800</v>
-      </c>
-      <c r="N26" s="3">
-        <v>1076100</v>
-      </c>
-      <c r="O26" s="3">
-        <v>1568900</v>
-      </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2348400</v>
+        <v>1805100</v>
       </c>
       <c r="E27" s="3">
-        <v>1941700</v>
+        <v>2317900</v>
       </c>
       <c r="F27" s="3">
-        <v>968900</v>
+        <v>1916500</v>
       </c>
       <c r="G27" s="3">
-        <v>1438200</v>
+        <v>956300</v>
       </c>
       <c r="H27" s="3">
-        <v>1449100</v>
+        <v>1419600</v>
       </c>
       <c r="I27" s="3">
-        <v>1035700</v>
+        <v>1430300</v>
       </c>
       <c r="J27" s="3">
+        <v>1022300</v>
+      </c>
+      <c r="K27" s="3">
         <v>812200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>648100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>312000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>120700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>955200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1437400</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1554,20 +1614,23 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>630700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-636700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>393900</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>456200</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2561000</v>
+        <v>2530900</v>
       </c>
       <c r="E32" s="3">
-        <v>2062800</v>
+        <v>2527700</v>
       </c>
       <c r="F32" s="3">
-        <v>2467400</v>
+        <v>2036000</v>
       </c>
       <c r="G32" s="3">
-        <v>2153200</v>
+        <v>2435400</v>
       </c>
       <c r="H32" s="3">
-        <v>1868800</v>
+        <v>2125300</v>
       </c>
       <c r="I32" s="3">
-        <v>1854800</v>
+        <v>1844600</v>
       </c>
       <c r="J32" s="3">
+        <v>1830700</v>
+      </c>
+      <c r="K32" s="3">
         <v>1983100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1626400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2059400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1823700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1177200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>578900</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2348400</v>
+        <v>1805100</v>
       </c>
       <c r="E33" s="3">
-        <v>1941700</v>
+        <v>2317900</v>
       </c>
       <c r="F33" s="3">
-        <v>968900</v>
+        <v>1916500</v>
       </c>
       <c r="G33" s="3">
-        <v>1438200</v>
+        <v>956300</v>
       </c>
       <c r="H33" s="3">
-        <v>1449100</v>
+        <v>1419600</v>
       </c>
       <c r="I33" s="3">
-        <v>1035700</v>
+        <v>1430300</v>
       </c>
       <c r="J33" s="3">
+        <v>1022300</v>
+      </c>
+      <c r="K33" s="3">
         <v>812200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>648100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>942700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-516000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1349000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1893700</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2348400</v>
+        <v>1805100</v>
       </c>
       <c r="E35" s="3">
-        <v>1941700</v>
+        <v>2317900</v>
       </c>
       <c r="F35" s="3">
-        <v>968900</v>
+        <v>1916500</v>
       </c>
       <c r="G35" s="3">
-        <v>1438200</v>
+        <v>956300</v>
       </c>
       <c r="H35" s="3">
-        <v>1449100</v>
+        <v>1419600</v>
       </c>
       <c r="I35" s="3">
-        <v>1035700</v>
+        <v>1430300</v>
       </c>
       <c r="J35" s="3">
+        <v>1022300</v>
+      </c>
+      <c r="K35" s="3">
         <v>812200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>648100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>942700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-516000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1349000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1893700</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,92 +1986,99 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>26279400</v>
+        <v>23125700</v>
       </c>
       <c r="E41" s="3">
-        <v>5703500</v>
+        <v>25938100</v>
       </c>
       <c r="F41" s="3">
-        <v>7269000</v>
+        <v>5629500</v>
       </c>
       <c r="G41" s="3">
-        <v>4826400</v>
+        <v>7174600</v>
       </c>
       <c r="H41" s="3">
-        <v>4885800</v>
+        <v>4763700</v>
       </c>
       <c r="I41" s="3">
-        <v>4658400</v>
+        <v>4822300</v>
       </c>
       <c r="J41" s="3">
+        <v>4597900</v>
+      </c>
+      <c r="K41" s="3">
         <v>5463200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4465200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4213200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9364800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4853800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5647100</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>42179700</v>
+        <v>43799200</v>
       </c>
       <c r="E42" s="3">
-        <v>45259000</v>
+        <v>41631900</v>
       </c>
       <c r="F42" s="3">
-        <v>40758300</v>
+        <v>44671200</v>
       </c>
       <c r="G42" s="3">
-        <v>34134400</v>
+        <v>40229000</v>
       </c>
       <c r="H42" s="3">
-        <v>27295300</v>
+        <v>33691100</v>
       </c>
       <c r="I42" s="3">
-        <v>18315800</v>
+        <v>26940900</v>
       </c>
       <c r="J42" s="3">
+        <v>18077900</v>
+      </c>
+      <c r="K42" s="3">
         <v>12152400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>10478600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>14255500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>39630600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>47429400</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2026,9 +2118,12 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2068,9 +2163,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2110,9 +2208,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2152,135 +2253,147 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1005300</v>
+        <v>1364500</v>
       </c>
       <c r="E47" s="3">
-        <v>1028100</v>
+        <v>992300</v>
       </c>
       <c r="F47" s="3">
-        <v>764800</v>
+        <v>1014700</v>
       </c>
       <c r="G47" s="3">
-        <v>620900</v>
+        <v>754900</v>
       </c>
       <c r="H47" s="3">
-        <v>278300</v>
+        <v>612800</v>
       </c>
       <c r="I47" s="3">
-        <v>321100</v>
+        <v>274700</v>
       </c>
       <c r="J47" s="3">
+        <v>317000</v>
+      </c>
+      <c r="K47" s="3">
         <v>338000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>476500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>525200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1621000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>871900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>816800</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2718600</v>
+        <v>2773600</v>
       </c>
       <c r="E48" s="3">
-        <v>2744400</v>
+        <v>2683300</v>
       </c>
       <c r="F48" s="3">
-        <v>2829500</v>
+        <v>2708800</v>
       </c>
       <c r="G48" s="3">
-        <v>2806600</v>
+        <v>2792700</v>
       </c>
       <c r="H48" s="3">
-        <v>2170800</v>
+        <v>2770200</v>
       </c>
       <c r="I48" s="3">
-        <v>2193600</v>
+        <v>2142600</v>
       </c>
       <c r="J48" s="3">
+        <v>2165100</v>
+      </c>
+      <c r="K48" s="3">
         <v>2168700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2088800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2315500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5236300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4968600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3197500</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>653800</v>
+        <v>757600</v>
       </c>
       <c r="E49" s="3">
-        <v>604700</v>
+        <v>645300</v>
       </c>
       <c r="F49" s="3">
-        <v>609900</v>
+        <v>596900</v>
       </c>
       <c r="G49" s="3">
-        <v>650000</v>
+        <v>602000</v>
       </c>
       <c r="H49" s="3">
-        <v>452200</v>
+        <v>641500</v>
       </c>
       <c r="I49" s="3">
-        <v>399300</v>
+        <v>446300</v>
       </c>
       <c r="J49" s="3">
+        <v>394100</v>
+      </c>
+      <c r="K49" s="3">
         <v>372500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>310700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>239500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>489400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>728100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>394100</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>340600</v>
+        <v>269000</v>
       </c>
       <c r="E52" s="3">
-        <v>60700</v>
+        <v>336200</v>
       </c>
       <c r="F52" s="3">
-        <v>86000</v>
+        <v>59900</v>
       </c>
       <c r="G52" s="3">
-        <v>40600</v>
+        <v>84900</v>
       </c>
       <c r="H52" s="3">
-        <v>110400</v>
+        <v>40000</v>
       </c>
       <c r="I52" s="3">
-        <v>253100</v>
+        <v>109000</v>
       </c>
       <c r="J52" s="3">
+        <v>249900</v>
+      </c>
+      <c r="K52" s="3">
         <v>235100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>169100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>215400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>77631000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>200600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>70400</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>369965000</v>
+        <v>378484000</v>
       </c>
       <c r="E54" s="3">
-        <v>344332000</v>
+        <v>365161000</v>
       </c>
       <c r="F54" s="3">
-        <v>307292000</v>
+        <v>339860000</v>
       </c>
       <c r="G54" s="3">
-        <v>278725000</v>
+        <v>303302000</v>
       </c>
       <c r="H54" s="3">
-        <v>262144000</v>
+        <v>275105000</v>
       </c>
       <c r="I54" s="3">
-        <v>243548000</v>
+        <v>258740000</v>
       </c>
       <c r="J54" s="3">
+        <v>240385000</v>
+      </c>
+      <c r="K54" s="3">
         <v>239226000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>215976000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>218827000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>310028000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>274766000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>275257000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,50 +2654,54 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8821300</v>
+        <v>9471700</v>
       </c>
       <c r="E57" s="3">
-        <v>11133900</v>
+        <v>8706700</v>
       </c>
       <c r="F57" s="3">
-        <v>3848500</v>
+        <v>10989300</v>
       </c>
       <c r="G57" s="3">
-        <v>6581000</v>
+        <v>3798500</v>
       </c>
       <c r="H57" s="3">
-        <v>10072800</v>
+        <v>6495500</v>
       </c>
       <c r="I57" s="3">
-        <v>5076300</v>
+        <v>9942000</v>
       </c>
       <c r="J57" s="3">
+        <v>5010400</v>
+      </c>
+      <c r="K57" s="3">
         <v>11404000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6198800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6717900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13975600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1000300</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2600,59 +2733,65 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>7098200</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3128400</v>
+        <v>3376700</v>
       </c>
       <c r="E59" s="3">
-        <v>2044500</v>
+        <v>3087800</v>
       </c>
       <c r="F59" s="3">
-        <v>1863500</v>
+        <v>2017900</v>
       </c>
       <c r="G59" s="3">
-        <v>2078200</v>
+        <v>1839300</v>
       </c>
       <c r="H59" s="3">
-        <v>1824100</v>
+        <v>2051200</v>
       </c>
       <c r="I59" s="3">
-        <v>1757500</v>
+        <v>1800400</v>
       </c>
       <c r="J59" s="3">
+        <v>1734700</v>
+      </c>
+      <c r="K59" s="3">
         <v>1714900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1487500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2140100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4189100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3097800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>241300</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2692,93 +2831,102 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>54074700</v>
+        <v>53441800</v>
       </c>
       <c r="E61" s="3">
-        <v>52880100</v>
+        <v>53372400</v>
       </c>
       <c r="F61" s="3">
-        <v>44312800</v>
+        <v>52193400</v>
       </c>
       <c r="G61" s="3">
-        <v>38164400</v>
+        <v>43737300</v>
       </c>
       <c r="H61" s="3">
-        <v>33796300</v>
+        <v>37668700</v>
       </c>
       <c r="I61" s="3">
-        <v>32324100</v>
+        <v>33357400</v>
       </c>
       <c r="J61" s="3">
+        <v>31904300</v>
+      </c>
+      <c r="K61" s="3">
         <v>29549800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>28996600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>31952700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>31315500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>44470300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>471900</v>
+        <v>975300</v>
       </c>
       <c r="E62" s="3">
-        <v>624500</v>
+        <v>465800</v>
       </c>
       <c r="F62" s="3">
-        <v>549900</v>
+        <v>616400</v>
       </c>
       <c r="G62" s="3">
-        <v>516500</v>
+        <v>542700</v>
       </c>
       <c r="H62" s="3">
-        <v>421000</v>
+        <v>509800</v>
       </c>
       <c r="I62" s="3">
-        <v>366800</v>
+        <v>415500</v>
       </c>
       <c r="J62" s="3">
+        <v>362100</v>
+      </c>
+      <c r="K62" s="3">
         <v>396700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>470400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>639400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1466000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1843300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1119700</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>347819000</v>
+        <v>354417000</v>
       </c>
       <c r="E66" s="3">
-        <v>324433000</v>
+        <v>343302000</v>
       </c>
       <c r="F66" s="3">
-        <v>289541000</v>
+        <v>320220000</v>
       </c>
       <c r="G66" s="3">
-        <v>262162000</v>
+        <v>285781000</v>
       </c>
       <c r="H66" s="3">
-        <v>245405000</v>
+        <v>258758000</v>
       </c>
       <c r="I66" s="3">
-        <v>227866000</v>
+        <v>242218000</v>
       </c>
       <c r="J66" s="3">
+        <v>224907000</v>
+      </c>
+      <c r="K66" s="3">
         <v>223528000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>201776000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>204261000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>293819000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>259061000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>259836000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>18287600</v>
+        <v>18989700</v>
       </c>
       <c r="E72" s="3">
-        <v>16472300</v>
+        <v>18050100</v>
       </c>
       <c r="F72" s="3">
-        <v>14836600</v>
+        <v>16258300</v>
       </c>
       <c r="G72" s="3">
-        <v>14263900</v>
+        <v>14643900</v>
       </c>
       <c r="H72" s="3">
-        <v>13186000</v>
+        <v>14078600</v>
       </c>
       <c r="I72" s="3">
-        <v>12027400</v>
+        <v>13014700</v>
       </c>
       <c r="J72" s="3">
+        <v>11871200</v>
+      </c>
+      <c r="K72" s="3">
         <v>11250900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10157300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11473900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>23865100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11660400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10932000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>22146700</v>
+        <v>24066800</v>
       </c>
       <c r="E76" s="3">
-        <v>19898400</v>
+        <v>21859000</v>
       </c>
       <c r="F76" s="3">
-        <v>17751300</v>
+        <v>19639900</v>
       </c>
       <c r="G76" s="3">
-        <v>16563000</v>
+        <v>17520700</v>
       </c>
       <c r="H76" s="3">
-        <v>16739700</v>
+        <v>16347900</v>
       </c>
       <c r="I76" s="3">
-        <v>15681700</v>
+        <v>16522300</v>
       </c>
       <c r="J76" s="3">
+        <v>15478100</v>
+      </c>
+      <c r="K76" s="3">
         <v>15697300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14199500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14566600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16209000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15704600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15421100</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2348400</v>
+        <v>1805100</v>
       </c>
       <c r="E81" s="3">
-        <v>1941700</v>
+        <v>2317900</v>
       </c>
       <c r="F81" s="3">
-        <v>968900</v>
+        <v>1916500</v>
       </c>
       <c r="G81" s="3">
-        <v>1438200</v>
+        <v>956300</v>
       </c>
       <c r="H81" s="3">
-        <v>1449100</v>
+        <v>1419600</v>
       </c>
       <c r="I81" s="3">
-        <v>1035700</v>
+        <v>1430300</v>
       </c>
       <c r="J81" s="3">
+        <v>1022300</v>
+      </c>
+      <c r="K81" s="3">
         <v>812200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>648100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>942700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-516000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1349000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1893700</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>715600</v>
+        <v>754800</v>
       </c>
       <c r="E83" s="3">
-        <v>609800</v>
+        <v>706300</v>
       </c>
       <c r="F83" s="3">
-        <v>412400</v>
+        <v>601800</v>
       </c>
       <c r="G83" s="3">
-        <v>389400</v>
+        <v>407000</v>
       </c>
       <c r="H83" s="3">
-        <v>209900</v>
+        <v>384300</v>
       </c>
       <c r="I83" s="3">
-        <v>181600</v>
+        <v>207100</v>
       </c>
       <c r="J83" s="3">
+        <v>179200</v>
+      </c>
+      <c r="K83" s="3">
         <v>194100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>178200</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>273400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>244500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>240800</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>14340600</v>
+        <v>1232700</v>
       </c>
       <c r="E89" s="3">
-        <v>2925800</v>
+        <v>14154300</v>
       </c>
       <c r="F89" s="3">
-        <v>2776600</v>
+        <v>2887800</v>
       </c>
       <c r="G89" s="3">
-        <v>1440200</v>
+        <v>2740500</v>
       </c>
       <c r="H89" s="3">
-        <v>7053300</v>
+        <v>1421500</v>
       </c>
       <c r="I89" s="3">
-        <v>-1523800</v>
+        <v>6961700</v>
       </c>
       <c r="J89" s="3">
+        <v>-1504000</v>
+      </c>
+      <c r="K89" s="3">
         <v>3777100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-284100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3234100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3633400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-121000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-942600</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-133100</v>
+        <v>-125200</v>
       </c>
       <c r="E91" s="3">
-        <v>-91800</v>
+        <v>-131400</v>
       </c>
       <c r="F91" s="3">
-        <v>-115000</v>
+        <v>-90600</v>
       </c>
       <c r="G91" s="3">
-        <v>-330800</v>
+        <v>-113500</v>
       </c>
       <c r="H91" s="3">
-        <v>-91400</v>
+        <v>-326500</v>
       </c>
       <c r="I91" s="3">
-        <v>-124900</v>
+        <v>-90200</v>
       </c>
       <c r="J91" s="3">
+        <v>-123300</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-95800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-129100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-145100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-212100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-204600</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5365900</v>
+        <v>-1713100</v>
       </c>
       <c r="E94" s="3">
-        <v>-8213500</v>
+        <v>-5296200</v>
       </c>
       <c r="F94" s="3">
-        <v>-1121400</v>
+        <v>-8106800</v>
       </c>
       <c r="G94" s="3">
-        <v>-6612900</v>
+        <v>-1106900</v>
       </c>
       <c r="H94" s="3">
-        <v>-8524800</v>
+        <v>-6527000</v>
       </c>
       <c r="I94" s="3">
-        <v>1450500</v>
+        <v>-8414100</v>
       </c>
       <c r="J94" s="3">
+        <v>1431600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-3253700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>942900</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>-357600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1975800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2124000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-504300</v>
+        <v>-743600</v>
       </c>
       <c r="E96" s="3">
-        <v>-283600</v>
+        <v>-497800</v>
       </c>
       <c r="F96" s="3">
-        <v>-389300</v>
+        <v>-280000</v>
       </c>
       <c r="G96" s="3">
-        <v>-337000</v>
+        <v>-384200</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-332600</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-129600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-373700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-306500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-344300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-288400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-177300</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1478200</v>
+        <v>-2173700</v>
       </c>
       <c r="E100" s="3">
-        <v>6988300</v>
+        <v>1459000</v>
       </c>
       <c r="F100" s="3">
-        <v>1822800</v>
+        <v>6897500</v>
       </c>
       <c r="G100" s="3">
-        <v>4751700</v>
+        <v>1799100</v>
       </c>
       <c r="H100" s="3">
-        <v>1167900</v>
+        <v>4690000</v>
       </c>
       <c r="I100" s="3">
-        <v>-47000</v>
+        <v>1152700</v>
       </c>
       <c r="J100" s="3">
+        <v>-46400</v>
+      </c>
+      <c r="K100" s="3">
         <v>256500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-356200</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>3803800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2248200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>154300</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>23800</v>
+        <v>-129300</v>
       </c>
       <c r="E101" s="3">
-        <v>817200</v>
+        <v>23500</v>
       </c>
       <c r="F101" s="3">
-        <v>-707100</v>
+        <v>806600</v>
       </c>
       <c r="G101" s="3">
-        <v>147400</v>
+        <v>-698000</v>
       </c>
       <c r="H101" s="3">
-        <v>180100</v>
+        <v>145500</v>
       </c>
       <c r="I101" s="3">
-        <v>-405500</v>
+        <v>177800</v>
       </c>
       <c r="J101" s="3">
+        <v>-400300</v>
+      </c>
+      <c r="K101" s="3">
         <v>-50400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>201600</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
         <v>-86400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-143800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>24700</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>10476700</v>
+        <v>-2783500</v>
       </c>
       <c r="E102" s="3">
-        <v>2517800</v>
+        <v>10340600</v>
       </c>
       <c r="F102" s="3">
-        <v>2770800</v>
+        <v>2485100</v>
       </c>
       <c r="G102" s="3">
-        <v>-273600</v>
+        <v>2734800</v>
       </c>
       <c r="H102" s="3">
-        <v>-123500</v>
+        <v>-270000</v>
       </c>
       <c r="I102" s="3">
-        <v>-525900</v>
+        <v>-121900</v>
       </c>
       <c r="J102" s="3">
+        <v>-519100</v>
+      </c>
+      <c r="K102" s="3">
         <v>729400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>504100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-243600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-273700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-537200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1360500</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/WF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WF_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>15687600</v>
+        <v>15068300</v>
       </c>
       <c r="E8" s="3">
-        <v>11137500</v>
+        <v>10697800</v>
       </c>
       <c r="F8" s="3">
-        <v>7520000</v>
+        <v>7223200</v>
       </c>
       <c r="G8" s="3">
-        <v>7238100</v>
+        <v>6952400</v>
       </c>
       <c r="H8" s="3">
-        <v>8038300</v>
+        <v>7721000</v>
       </c>
       <c r="I8" s="3">
-        <v>7360200</v>
+        <v>7069700</v>
       </c>
       <c r="J8" s="3">
-        <v>6498500</v>
+        <v>6242000</v>
       </c>
       <c r="K8" s="3">
         <v>6554500</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-386400</v>
+        <v>-371200</v>
       </c>
       <c r="E15" s="3">
-        <v>-399600</v>
+        <v>-383800</v>
       </c>
       <c r="F15" s="3">
-        <v>-400500</v>
+        <v>-384700</v>
       </c>
       <c r="G15" s="3">
-        <v>-398000</v>
+        <v>-382300</v>
       </c>
       <c r="H15" s="3">
-        <v>-367400</v>
+        <v>-352900</v>
       </c>
       <c r="I15" s="3">
-        <v>-167800</v>
+        <v>-161200</v>
       </c>
       <c r="J15" s="3">
-        <v>-142500</v>
+        <v>-136900</v>
       </c>
       <c r="K15" s="3">
         <v>-194100</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10483400</v>
+        <v>10069600</v>
       </c>
       <c r="E17" s="3">
-        <v>5200900</v>
+        <v>4995600</v>
       </c>
       <c r="F17" s="3">
-        <v>2634600</v>
+        <v>2530600</v>
       </c>
       <c r="G17" s="3">
-        <v>3281800</v>
+        <v>3152300</v>
       </c>
       <c r="H17" s="3">
-        <v>3843600</v>
+        <v>3691800</v>
       </c>
       <c r="I17" s="3">
-        <v>3384000</v>
+        <v>3250400</v>
       </c>
       <c r="J17" s="3">
-        <v>3186200</v>
+        <v>3060400</v>
       </c>
       <c r="K17" s="3">
         <v>3375300</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>5204200</v>
+        <v>4998800</v>
       </c>
       <c r="E18" s="3">
-        <v>5936600</v>
+        <v>5702300</v>
       </c>
       <c r="F18" s="3">
-        <v>4885400</v>
+        <v>4692600</v>
       </c>
       <c r="G18" s="3">
-        <v>3956300</v>
+        <v>3800100</v>
       </c>
       <c r="H18" s="3">
-        <v>4194800</v>
+        <v>4029200</v>
       </c>
       <c r="I18" s="3">
-        <v>3976300</v>
+        <v>3819300</v>
       </c>
       <c r="J18" s="3">
-        <v>3312400</v>
+        <v>3181600</v>
       </c>
       <c r="K18" s="3">
         <v>3179200</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2530900</v>
+        <v>-2431000</v>
       </c>
       <c r="E20" s="3">
-        <v>-2527700</v>
+        <v>-2427900</v>
       </c>
       <c r="F20" s="3">
-        <v>-2036000</v>
+        <v>-1955600</v>
       </c>
       <c r="G20" s="3">
-        <v>-2435400</v>
+        <v>-2339200</v>
       </c>
       <c r="H20" s="3">
-        <v>-2125300</v>
+        <v>-2041400</v>
       </c>
       <c r="I20" s="3">
-        <v>-1844600</v>
+        <v>-1771700</v>
       </c>
       <c r="J20" s="3">
-        <v>-1830700</v>
+        <v>-1758500</v>
       </c>
       <c r="K20" s="3">
         <v>-1983100</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3428100</v>
+        <v>3292800</v>
       </c>
       <c r="E21" s="3">
-        <v>4115200</v>
+        <v>3952700</v>
       </c>
       <c r="F21" s="3">
-        <v>3451300</v>
+        <v>3315000</v>
       </c>
       <c r="G21" s="3">
-        <v>1928000</v>
+        <v>1851900</v>
       </c>
       <c r="H21" s="3">
-        <v>2453900</v>
+        <v>2357000</v>
       </c>
       <c r="I21" s="3">
-        <v>2338800</v>
+        <v>2246500</v>
       </c>
       <c r="J21" s="3">
-        <v>1660800</v>
+        <v>1595300</v>
       </c>
       <c r="K21" s="3">
         <v>1390200</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2673300</v>
+        <v>2567700</v>
       </c>
       <c r="E23" s="3">
-        <v>3408900</v>
+        <v>3274300</v>
       </c>
       <c r="F23" s="3">
-        <v>2849400</v>
+        <v>2736900</v>
       </c>
       <c r="G23" s="3">
-        <v>1521000</v>
+        <v>1460900</v>
       </c>
       <c r="H23" s="3">
-        <v>2069500</v>
+        <v>1987800</v>
       </c>
       <c r="I23" s="3">
-        <v>2131700</v>
+        <v>2047600</v>
       </c>
       <c r="J23" s="3">
-        <v>1481600</v>
+        <v>1423100</v>
       </c>
       <c r="K23" s="3">
         <v>1196100</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>676800</v>
+        <v>650100</v>
       </c>
       <c r="E24" s="3">
-        <v>882700</v>
+        <v>847800</v>
       </c>
       <c r="F24" s="3">
-        <v>715800</v>
+        <v>687600</v>
       </c>
       <c r="G24" s="3">
-        <v>369400</v>
+        <v>354800</v>
       </c>
       <c r="H24" s="3">
-        <v>520900</v>
+        <v>500400</v>
       </c>
       <c r="I24" s="3">
-        <v>572400</v>
+        <v>549900</v>
       </c>
       <c r="J24" s="3">
-        <v>318800</v>
+        <v>306200</v>
       </c>
       <c r="K24" s="3">
         <v>212400</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1996400</v>
+        <v>1917600</v>
       </c>
       <c r="E26" s="3">
-        <v>2526200</v>
+        <v>2426500</v>
       </c>
       <c r="F26" s="3">
-        <v>2133600</v>
+        <v>2049400</v>
       </c>
       <c r="G26" s="3">
-        <v>1151600</v>
+        <v>1106100</v>
       </c>
       <c r="H26" s="3">
-        <v>1548600</v>
+        <v>1487400</v>
       </c>
       <c r="I26" s="3">
-        <v>1559300</v>
+        <v>1497700</v>
       </c>
       <c r="J26" s="3">
-        <v>1162900</v>
+        <v>1117000</v>
       </c>
       <c r="K26" s="3">
         <v>983700</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1805100</v>
+        <v>1733900</v>
       </c>
       <c r="E27" s="3">
-        <v>2317900</v>
+        <v>2226400</v>
       </c>
       <c r="F27" s="3">
-        <v>1916500</v>
+        <v>1840800</v>
       </c>
       <c r="G27" s="3">
-        <v>956300</v>
+        <v>918600</v>
       </c>
       <c r="H27" s="3">
-        <v>1419600</v>
+        <v>1363500</v>
       </c>
       <c r="I27" s="3">
-        <v>1430300</v>
+        <v>1373900</v>
       </c>
       <c r="J27" s="3">
-        <v>1022300</v>
+        <v>981900</v>
       </c>
       <c r="K27" s="3">
         <v>812200</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2530900</v>
+        <v>2431000</v>
       </c>
       <c r="E32" s="3">
-        <v>2527700</v>
+        <v>2427900</v>
       </c>
       <c r="F32" s="3">
-        <v>2036000</v>
+        <v>1955600</v>
       </c>
       <c r="G32" s="3">
-        <v>2435400</v>
+        <v>2339200</v>
       </c>
       <c r="H32" s="3">
-        <v>2125300</v>
+        <v>2041400</v>
       </c>
       <c r="I32" s="3">
-        <v>1844600</v>
+        <v>1771700</v>
       </c>
       <c r="J32" s="3">
-        <v>1830700</v>
+        <v>1758500</v>
       </c>
       <c r="K32" s="3">
         <v>1983100</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1805100</v>
+        <v>1733900</v>
       </c>
       <c r="E33" s="3">
-        <v>2317900</v>
+        <v>2226400</v>
       </c>
       <c r="F33" s="3">
-        <v>1916500</v>
+        <v>1840800</v>
       </c>
       <c r="G33" s="3">
-        <v>956300</v>
+        <v>918600</v>
       </c>
       <c r="H33" s="3">
-        <v>1419600</v>
+        <v>1363500</v>
       </c>
       <c r="I33" s="3">
-        <v>1430300</v>
+        <v>1373900</v>
       </c>
       <c r="J33" s="3">
-        <v>1022300</v>
+        <v>981900</v>
       </c>
       <c r="K33" s="3">
         <v>812200</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1805100</v>
+        <v>1733900</v>
       </c>
       <c r="E35" s="3">
-        <v>2317900</v>
+        <v>2226400</v>
       </c>
       <c r="F35" s="3">
-        <v>1916500</v>
+        <v>1840800</v>
       </c>
       <c r="G35" s="3">
-        <v>956300</v>
+        <v>918600</v>
       </c>
       <c r="H35" s="3">
-        <v>1419600</v>
+        <v>1363500</v>
       </c>
       <c r="I35" s="3">
-        <v>1430300</v>
+        <v>1373900</v>
       </c>
       <c r="J35" s="3">
-        <v>1022300</v>
+        <v>981900</v>
       </c>
       <c r="K35" s="3">
         <v>812200</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>23125700</v>
+        <v>22212800</v>
       </c>
       <c r="E41" s="3">
-        <v>25938100</v>
+        <v>24914300</v>
       </c>
       <c r="F41" s="3">
-        <v>5629500</v>
+        <v>5407200</v>
       </c>
       <c r="G41" s="3">
-        <v>7174600</v>
+        <v>6891300</v>
       </c>
       <c r="H41" s="3">
-        <v>4763700</v>
+        <v>4575700</v>
       </c>
       <c r="I41" s="3">
-        <v>4822300</v>
+        <v>4632000</v>
       </c>
       <c r="J41" s="3">
-        <v>4597900</v>
+        <v>4416400</v>
       </c>
       <c r="K41" s="3">
         <v>5463200</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>43799200</v>
+        <v>42070300</v>
       </c>
       <c r="E42" s="3">
-        <v>41631900</v>
+        <v>39988600</v>
       </c>
       <c r="F42" s="3">
-        <v>44671200</v>
+        <v>42907900</v>
       </c>
       <c r="G42" s="3">
-        <v>40229000</v>
+        <v>38641000</v>
       </c>
       <c r="H42" s="3">
-        <v>33691100</v>
+        <v>32361200</v>
       </c>
       <c r="I42" s="3">
-        <v>26940900</v>
+        <v>25877400</v>
       </c>
       <c r="J42" s="3">
-        <v>18077900</v>
+        <v>17364300</v>
       </c>
       <c r="K42" s="3">
         <v>12152400</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1364500</v>
+        <v>1310600</v>
       </c>
       <c r="E47" s="3">
-        <v>992300</v>
+        <v>953100</v>
       </c>
       <c r="F47" s="3">
-        <v>1014700</v>
+        <v>974700</v>
       </c>
       <c r="G47" s="3">
-        <v>754900</v>
+        <v>725100</v>
       </c>
       <c r="H47" s="3">
-        <v>612800</v>
+        <v>588600</v>
       </c>
       <c r="I47" s="3">
-        <v>274700</v>
+        <v>263800</v>
       </c>
       <c r="J47" s="3">
-        <v>317000</v>
+        <v>304400</v>
       </c>
       <c r="K47" s="3">
         <v>338000</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2773600</v>
+        <v>2664200</v>
       </c>
       <c r="E48" s="3">
-        <v>2683300</v>
+        <v>2577400</v>
       </c>
       <c r="F48" s="3">
-        <v>2708800</v>
+        <v>2601900</v>
       </c>
       <c r="G48" s="3">
-        <v>2792700</v>
+        <v>2682500</v>
       </c>
       <c r="H48" s="3">
-        <v>2770200</v>
+        <v>2660800</v>
       </c>
       <c r="I48" s="3">
-        <v>2142600</v>
+        <v>2058000</v>
       </c>
       <c r="J48" s="3">
-        <v>2165100</v>
+        <v>2079700</v>
       </c>
       <c r="K48" s="3">
         <v>2168700</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>757600</v>
+        <v>727700</v>
       </c>
       <c r="E49" s="3">
-        <v>645300</v>
+        <v>619900</v>
       </c>
       <c r="F49" s="3">
-        <v>596900</v>
+        <v>573300</v>
       </c>
       <c r="G49" s="3">
-        <v>602000</v>
+        <v>578200</v>
       </c>
       <c r="H49" s="3">
-        <v>641500</v>
+        <v>616200</v>
       </c>
       <c r="I49" s="3">
-        <v>446300</v>
+        <v>428700</v>
       </c>
       <c r="J49" s="3">
-        <v>394100</v>
+        <v>378600</v>
       </c>
       <c r="K49" s="3">
         <v>372500</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>269000</v>
+        <v>258400</v>
       </c>
       <c r="E52" s="3">
-        <v>336200</v>
+        <v>322900</v>
       </c>
       <c r="F52" s="3">
-        <v>59900</v>
+        <v>57500</v>
       </c>
       <c r="G52" s="3">
-        <v>84900</v>
+        <v>81600</v>
       </c>
       <c r="H52" s="3">
-        <v>40000</v>
+        <v>38500</v>
       </c>
       <c r="I52" s="3">
-        <v>109000</v>
+        <v>104700</v>
       </c>
       <c r="J52" s="3">
-        <v>249900</v>
+        <v>240000</v>
       </c>
       <c r="K52" s="3">
         <v>235100</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>378484000</v>
+        <v>363544000</v>
       </c>
       <c r="E54" s="3">
-        <v>365161000</v>
+        <v>350746000</v>
       </c>
       <c r="F54" s="3">
-        <v>339860000</v>
+        <v>326444000</v>
       </c>
       <c r="G54" s="3">
-        <v>303302000</v>
+        <v>291329000</v>
       </c>
       <c r="H54" s="3">
-        <v>275105000</v>
+        <v>264246000</v>
       </c>
       <c r="I54" s="3">
-        <v>258740000</v>
+        <v>248526000</v>
       </c>
       <c r="J54" s="3">
-        <v>240385000</v>
+        <v>230896000</v>
       </c>
       <c r="K54" s="3">
         <v>239226000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9471700</v>
+        <v>9097800</v>
       </c>
       <c r="E57" s="3">
-        <v>8706700</v>
+        <v>8363000</v>
       </c>
       <c r="F57" s="3">
-        <v>10989300</v>
+        <v>10555500</v>
       </c>
       <c r="G57" s="3">
-        <v>3798500</v>
+        <v>3648600</v>
       </c>
       <c r="H57" s="3">
-        <v>6495500</v>
+        <v>6239100</v>
       </c>
       <c r="I57" s="3">
-        <v>9942000</v>
+        <v>9549500</v>
       </c>
       <c r="J57" s="3">
-        <v>5010400</v>
+        <v>4812600</v>
       </c>
       <c r="K57" s="3">
         <v>11404000</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3376700</v>
+        <v>3243400</v>
       </c>
       <c r="E59" s="3">
-        <v>3087800</v>
+        <v>2965900</v>
       </c>
       <c r="F59" s="3">
-        <v>2017900</v>
+        <v>1938200</v>
       </c>
       <c r="G59" s="3">
-        <v>1839300</v>
+        <v>1766700</v>
       </c>
       <c r="H59" s="3">
-        <v>2051200</v>
+        <v>1970200</v>
       </c>
       <c r="I59" s="3">
-        <v>1800400</v>
+        <v>1729300</v>
       </c>
       <c r="J59" s="3">
-        <v>1734700</v>
+        <v>1666200</v>
       </c>
       <c r="K59" s="3">
         <v>1714900</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>53441800</v>
+        <v>51332300</v>
       </c>
       <c r="E61" s="3">
-        <v>53372400</v>
+        <v>51265600</v>
       </c>
       <c r="F61" s="3">
-        <v>52193400</v>
+        <v>50133100</v>
       </c>
       <c r="G61" s="3">
-        <v>43737300</v>
+        <v>42010900</v>
       </c>
       <c r="H61" s="3">
-        <v>37668700</v>
+        <v>36181800</v>
       </c>
       <c r="I61" s="3">
-        <v>33357400</v>
+        <v>32040700</v>
       </c>
       <c r="J61" s="3">
-        <v>31904300</v>
+        <v>30644900</v>
       </c>
       <c r="K61" s="3">
         <v>29549800</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>975300</v>
+        <v>936800</v>
       </c>
       <c r="E62" s="3">
-        <v>465800</v>
+        <v>447400</v>
       </c>
       <c r="F62" s="3">
-        <v>616400</v>
+        <v>592100</v>
       </c>
       <c r="G62" s="3">
-        <v>542700</v>
+        <v>521300</v>
       </c>
       <c r="H62" s="3">
-        <v>509800</v>
+        <v>489700</v>
       </c>
       <c r="I62" s="3">
-        <v>415500</v>
+        <v>399100</v>
       </c>
       <c r="J62" s="3">
-        <v>362100</v>
+        <v>347800</v>
       </c>
       <c r="K62" s="3">
         <v>396700</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>354417000</v>
+        <v>340427000</v>
       </c>
       <c r="E66" s="3">
-        <v>343302000</v>
+        <v>329750000</v>
       </c>
       <c r="F66" s="3">
-        <v>320220000</v>
+        <v>307580000</v>
       </c>
       <c r="G66" s="3">
-        <v>285781000</v>
+        <v>274500000</v>
       </c>
       <c r="H66" s="3">
-        <v>258758000</v>
+        <v>248543000</v>
       </c>
       <c r="I66" s="3">
-        <v>242218000</v>
+        <v>232656000</v>
       </c>
       <c r="J66" s="3">
-        <v>224907000</v>
+        <v>216029000</v>
       </c>
       <c r="K66" s="3">
         <v>223528000</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>18989700</v>
+        <v>18240100</v>
       </c>
       <c r="E72" s="3">
-        <v>18050100</v>
+        <v>17337600</v>
       </c>
       <c r="F72" s="3">
-        <v>16258300</v>
+        <v>15616600</v>
       </c>
       <c r="G72" s="3">
-        <v>14643900</v>
+        <v>14065800</v>
       </c>
       <c r="H72" s="3">
-        <v>14078600</v>
+        <v>13522900</v>
       </c>
       <c r="I72" s="3">
-        <v>13014700</v>
+        <v>12501000</v>
       </c>
       <c r="J72" s="3">
-        <v>11871200</v>
+        <v>11402600</v>
       </c>
       <c r="K72" s="3">
         <v>11250900</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>24066800</v>
+        <v>23116800</v>
       </c>
       <c r="E76" s="3">
-        <v>21859000</v>
+        <v>20996200</v>
       </c>
       <c r="F76" s="3">
-        <v>19639900</v>
+        <v>18864700</v>
       </c>
       <c r="G76" s="3">
-        <v>17520700</v>
+        <v>16829100</v>
       </c>
       <c r="H76" s="3">
-        <v>16347900</v>
+        <v>15702600</v>
       </c>
       <c r="I76" s="3">
-        <v>16522300</v>
+        <v>15870100</v>
       </c>
       <c r="J76" s="3">
-        <v>15478100</v>
+        <v>14867100</v>
       </c>
       <c r="K76" s="3">
         <v>15697300</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1805100</v>
+        <v>1733900</v>
       </c>
       <c r="E81" s="3">
-        <v>2317900</v>
+        <v>2226400</v>
       </c>
       <c r="F81" s="3">
-        <v>1916500</v>
+        <v>1840800</v>
       </c>
       <c r="G81" s="3">
-        <v>956300</v>
+        <v>918600</v>
       </c>
       <c r="H81" s="3">
-        <v>1419600</v>
+        <v>1363500</v>
       </c>
       <c r="I81" s="3">
-        <v>1430300</v>
+        <v>1373900</v>
       </c>
       <c r="J81" s="3">
-        <v>1022300</v>
+        <v>981900</v>
       </c>
       <c r="K81" s="3">
         <v>812200</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>754800</v>
+        <v>725000</v>
       </c>
       <c r="E83" s="3">
-        <v>706300</v>
+        <v>678400</v>
       </c>
       <c r="F83" s="3">
-        <v>601800</v>
+        <v>578100</v>
       </c>
       <c r="G83" s="3">
-        <v>407000</v>
+        <v>391000</v>
       </c>
       <c r="H83" s="3">
-        <v>384300</v>
+        <v>369200</v>
       </c>
       <c r="I83" s="3">
-        <v>207100</v>
+        <v>199000</v>
       </c>
       <c r="J83" s="3">
-        <v>179200</v>
+        <v>172100</v>
       </c>
       <c r="K83" s="3">
         <v>194100</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1232700</v>
+        <v>1184000</v>
       </c>
       <c r="E89" s="3">
-        <v>14154300</v>
+        <v>13595600</v>
       </c>
       <c r="F89" s="3">
-        <v>2887800</v>
+        <v>2773800</v>
       </c>
       <c r="G89" s="3">
-        <v>2740500</v>
+        <v>2632400</v>
       </c>
       <c r="H89" s="3">
-        <v>1421500</v>
+        <v>1365400</v>
       </c>
       <c r="I89" s="3">
-        <v>6961700</v>
+        <v>6686900</v>
       </c>
       <c r="J89" s="3">
-        <v>-1504000</v>
+        <v>-1444700</v>
       </c>
       <c r="K89" s="3">
         <v>3777100</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-125200</v>
+        <v>-120200</v>
       </c>
       <c r="E91" s="3">
-        <v>-131400</v>
+        <v>-126200</v>
       </c>
       <c r="F91" s="3">
-        <v>-90600</v>
+        <v>-87100</v>
       </c>
       <c r="G91" s="3">
-        <v>-113500</v>
+        <v>-109000</v>
       </c>
       <c r="H91" s="3">
-        <v>-326500</v>
+        <v>-313600</v>
       </c>
       <c r="I91" s="3">
-        <v>-90200</v>
+        <v>-86600</v>
       </c>
       <c r="J91" s="3">
-        <v>-123300</v>
+        <v>-118400</v>
       </c>
       <c r="K91" s="3">
         <v>-100900</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1713100</v>
+        <v>-1645500</v>
       </c>
       <c r="E94" s="3">
-        <v>-5296200</v>
+        <v>-5087100</v>
       </c>
       <c r="F94" s="3">
-        <v>-8106800</v>
+        <v>-7786800</v>
       </c>
       <c r="G94" s="3">
-        <v>-1106900</v>
+        <v>-1063200</v>
       </c>
       <c r="H94" s="3">
-        <v>-6527000</v>
+        <v>-6269300</v>
       </c>
       <c r="I94" s="3">
-        <v>-8414100</v>
+        <v>-8082000</v>
       </c>
       <c r="J94" s="3">
-        <v>1431600</v>
+        <v>1375100</v>
       </c>
       <c r="K94" s="3">
         <v>-3253700</v>
@@ -4227,19 +4227,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-743600</v>
+        <v>-714200</v>
       </c>
       <c r="E96" s="3">
-        <v>-497800</v>
+        <v>-478100</v>
       </c>
       <c r="F96" s="3">
-        <v>-280000</v>
+        <v>-268900</v>
       </c>
       <c r="G96" s="3">
-        <v>-384200</v>
+        <v>-369100</v>
       </c>
       <c r="H96" s="3">
-        <v>-332600</v>
+        <v>-319500</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2173700</v>
+        <v>-2087900</v>
       </c>
       <c r="E100" s="3">
-        <v>1459000</v>
+        <v>1401400</v>
       </c>
       <c r="F100" s="3">
-        <v>6897500</v>
+        <v>6625300</v>
       </c>
       <c r="G100" s="3">
-        <v>1799100</v>
+        <v>1728100</v>
       </c>
       <c r="H100" s="3">
-        <v>4690000</v>
+        <v>4504800</v>
       </c>
       <c r="I100" s="3">
-        <v>1152700</v>
+        <v>1107200</v>
       </c>
       <c r="J100" s="3">
-        <v>-46400</v>
+        <v>-44600</v>
       </c>
       <c r="K100" s="3">
         <v>256500</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-129300</v>
+        <v>-124200</v>
       </c>
       <c r="E101" s="3">
-        <v>23500</v>
+        <v>22500</v>
       </c>
       <c r="F101" s="3">
-        <v>806600</v>
+        <v>774700</v>
       </c>
       <c r="G101" s="3">
-        <v>-698000</v>
+        <v>-670400</v>
       </c>
       <c r="H101" s="3">
-        <v>145500</v>
+        <v>139800</v>
       </c>
       <c r="I101" s="3">
-        <v>177800</v>
+        <v>170800</v>
       </c>
       <c r="J101" s="3">
-        <v>-400300</v>
+        <v>-384500</v>
       </c>
       <c r="K101" s="3">
         <v>-50400</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2783500</v>
+        <v>-2673600</v>
       </c>
       <c r="E102" s="3">
-        <v>10340600</v>
+        <v>9932400</v>
       </c>
       <c r="F102" s="3">
-        <v>2485100</v>
+        <v>2387000</v>
       </c>
       <c r="G102" s="3">
-        <v>2734800</v>
+        <v>2626800</v>
       </c>
       <c r="H102" s="3">
-        <v>-270000</v>
+        <v>-259400</v>
       </c>
       <c r="I102" s="3">
-        <v>-121900</v>
+        <v>-117100</v>
       </c>
       <c r="J102" s="3">
-        <v>-519100</v>
+        <v>-498600</v>
       </c>
       <c r="K102" s="3">
         <v>729400</v>

--- a/AAII_Financials/Yearly/WF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WF_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>15068300</v>
+        <v>15481200</v>
       </c>
       <c r="E8" s="3">
-        <v>10697800</v>
+        <v>10990900</v>
       </c>
       <c r="F8" s="3">
-        <v>7223200</v>
+        <v>7421100</v>
       </c>
       <c r="G8" s="3">
-        <v>6952400</v>
+        <v>7142900</v>
       </c>
       <c r="H8" s="3">
-        <v>7721000</v>
+        <v>7932600</v>
       </c>
       <c r="I8" s="3">
-        <v>7069700</v>
+        <v>7263400</v>
       </c>
       <c r="J8" s="3">
-        <v>6242000</v>
+        <v>6413000</v>
       </c>
       <c r="K8" s="3">
         <v>6554500</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-371200</v>
+        <v>-381300</v>
       </c>
       <c r="E15" s="3">
-        <v>-383800</v>
+        <v>-394300</v>
       </c>
       <c r="F15" s="3">
-        <v>-384700</v>
+        <v>-395200</v>
       </c>
       <c r="G15" s="3">
-        <v>-382300</v>
+        <v>-392700</v>
       </c>
       <c r="H15" s="3">
-        <v>-352900</v>
+        <v>-362600</v>
       </c>
       <c r="I15" s="3">
-        <v>-161200</v>
+        <v>-165600</v>
       </c>
       <c r="J15" s="3">
-        <v>-136900</v>
+        <v>-140600</v>
       </c>
       <c r="K15" s="3">
         <v>-194100</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10069600</v>
+        <v>10345400</v>
       </c>
       <c r="E17" s="3">
-        <v>4995600</v>
+        <v>5132400</v>
       </c>
       <c r="F17" s="3">
-        <v>2530600</v>
+        <v>2599900</v>
       </c>
       <c r="G17" s="3">
-        <v>3152300</v>
+        <v>3238600</v>
       </c>
       <c r="H17" s="3">
-        <v>3691800</v>
+        <v>3793000</v>
       </c>
       <c r="I17" s="3">
-        <v>3250400</v>
+        <v>3339400</v>
       </c>
       <c r="J17" s="3">
-        <v>3060400</v>
+        <v>3144200</v>
       </c>
       <c r="K17" s="3">
         <v>3375300</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4998800</v>
+        <v>5135700</v>
       </c>
       <c r="E18" s="3">
-        <v>5702300</v>
+        <v>5858500</v>
       </c>
       <c r="F18" s="3">
-        <v>4692600</v>
+        <v>4821100</v>
       </c>
       <c r="G18" s="3">
-        <v>3800100</v>
+        <v>3904300</v>
       </c>
       <c r="H18" s="3">
-        <v>4029200</v>
+        <v>4139600</v>
       </c>
       <c r="I18" s="3">
-        <v>3819300</v>
+        <v>3923900</v>
       </c>
       <c r="J18" s="3">
-        <v>3181600</v>
+        <v>3268800</v>
       </c>
       <c r="K18" s="3">
         <v>3179200</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2431000</v>
+        <v>-2497600</v>
       </c>
       <c r="E20" s="3">
-        <v>-2427900</v>
+        <v>-2494400</v>
       </c>
       <c r="F20" s="3">
-        <v>-1955600</v>
+        <v>-2009200</v>
       </c>
       <c r="G20" s="3">
-        <v>-2339200</v>
+        <v>-2403300</v>
       </c>
       <c r="H20" s="3">
-        <v>-2041400</v>
+        <v>-2097300</v>
       </c>
       <c r="I20" s="3">
-        <v>-1771700</v>
+        <v>-1820300</v>
       </c>
       <c r="J20" s="3">
-        <v>-1758500</v>
+        <v>-1806700</v>
       </c>
       <c r="K20" s="3">
         <v>-1983100</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3292800</v>
+        <v>3383000</v>
       </c>
       <c r="E21" s="3">
-        <v>3952700</v>
+        <v>4061000</v>
       </c>
       <c r="F21" s="3">
-        <v>3315000</v>
+        <v>3405900</v>
       </c>
       <c r="G21" s="3">
-        <v>1851900</v>
+        <v>1902600</v>
       </c>
       <c r="H21" s="3">
-        <v>2357000</v>
+        <v>2421600</v>
       </c>
       <c r="I21" s="3">
-        <v>2246500</v>
+        <v>2308100</v>
       </c>
       <c r="J21" s="3">
-        <v>1595300</v>
+        <v>1639000</v>
       </c>
       <c r="K21" s="3">
         <v>1390200</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2567700</v>
+        <v>2638100</v>
       </c>
       <c r="E23" s="3">
-        <v>3274300</v>
+        <v>3364000</v>
       </c>
       <c r="F23" s="3">
-        <v>2736900</v>
+        <v>2811900</v>
       </c>
       <c r="G23" s="3">
-        <v>1460900</v>
+        <v>1500900</v>
       </c>
       <c r="H23" s="3">
-        <v>1987800</v>
+        <v>2042300</v>
       </c>
       <c r="I23" s="3">
-        <v>2047600</v>
+        <v>2103700</v>
       </c>
       <c r="J23" s="3">
-        <v>1423100</v>
+        <v>1462100</v>
       </c>
       <c r="K23" s="3">
         <v>1196100</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>650100</v>
+        <v>667900</v>
       </c>
       <c r="E24" s="3">
-        <v>847800</v>
+        <v>871000</v>
       </c>
       <c r="F24" s="3">
-        <v>687600</v>
+        <v>706400</v>
       </c>
       <c r="G24" s="3">
-        <v>354800</v>
+        <v>364500</v>
       </c>
       <c r="H24" s="3">
-        <v>500400</v>
+        <v>514100</v>
       </c>
       <c r="I24" s="3">
-        <v>549900</v>
+        <v>564900</v>
       </c>
       <c r="J24" s="3">
-        <v>306200</v>
+        <v>314600</v>
       </c>
       <c r="K24" s="3">
         <v>212400</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1917600</v>
+        <v>1970200</v>
       </c>
       <c r="E26" s="3">
-        <v>2426500</v>
+        <v>2493000</v>
       </c>
       <c r="F26" s="3">
-        <v>2049400</v>
+        <v>2105500</v>
       </c>
       <c r="G26" s="3">
-        <v>1106100</v>
+        <v>1136400</v>
       </c>
       <c r="H26" s="3">
-        <v>1487400</v>
+        <v>1528200</v>
       </c>
       <c r="I26" s="3">
-        <v>1497700</v>
+        <v>1538700</v>
       </c>
       <c r="J26" s="3">
-        <v>1117000</v>
+        <v>1147600</v>
       </c>
       <c r="K26" s="3">
         <v>983700</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1733900</v>
+        <v>1781400</v>
       </c>
       <c r="E27" s="3">
-        <v>2226400</v>
+        <v>2287400</v>
       </c>
       <c r="F27" s="3">
-        <v>1840800</v>
+        <v>1891300</v>
       </c>
       <c r="G27" s="3">
-        <v>918600</v>
+        <v>943800</v>
       </c>
       <c r="H27" s="3">
-        <v>1363500</v>
+        <v>1400900</v>
       </c>
       <c r="I27" s="3">
-        <v>1373900</v>
+        <v>1411500</v>
       </c>
       <c r="J27" s="3">
-        <v>981900</v>
+        <v>1008800</v>
       </c>
       <c r="K27" s="3">
         <v>812200</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2431000</v>
+        <v>2497600</v>
       </c>
       <c r="E32" s="3">
-        <v>2427900</v>
+        <v>2494400</v>
       </c>
       <c r="F32" s="3">
-        <v>1955600</v>
+        <v>2009200</v>
       </c>
       <c r="G32" s="3">
-        <v>2339200</v>
+        <v>2403300</v>
       </c>
       <c r="H32" s="3">
-        <v>2041400</v>
+        <v>2097300</v>
       </c>
       <c r="I32" s="3">
-        <v>1771700</v>
+        <v>1820300</v>
       </c>
       <c r="J32" s="3">
-        <v>1758500</v>
+        <v>1806700</v>
       </c>
       <c r="K32" s="3">
         <v>1983100</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1733900</v>
+        <v>1781400</v>
       </c>
       <c r="E33" s="3">
-        <v>2226400</v>
+        <v>2287400</v>
       </c>
       <c r="F33" s="3">
-        <v>1840800</v>
+        <v>1891300</v>
       </c>
       <c r="G33" s="3">
-        <v>918600</v>
+        <v>943800</v>
       </c>
       <c r="H33" s="3">
-        <v>1363500</v>
+        <v>1400900</v>
       </c>
       <c r="I33" s="3">
-        <v>1373900</v>
+        <v>1411500</v>
       </c>
       <c r="J33" s="3">
-        <v>981900</v>
+        <v>1008800</v>
       </c>
       <c r="K33" s="3">
         <v>812200</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1733900</v>
+        <v>1781400</v>
       </c>
       <c r="E35" s="3">
-        <v>2226400</v>
+        <v>2287400</v>
       </c>
       <c r="F35" s="3">
-        <v>1840800</v>
+        <v>1891300</v>
       </c>
       <c r="G35" s="3">
-        <v>918600</v>
+        <v>943800</v>
       </c>
       <c r="H35" s="3">
-        <v>1363500</v>
+        <v>1400900</v>
       </c>
       <c r="I35" s="3">
-        <v>1373900</v>
+        <v>1411500</v>
       </c>
       <c r="J35" s="3">
-        <v>981900</v>
+        <v>1008800</v>
       </c>
       <c r="K35" s="3">
         <v>812200</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>22212800</v>
+        <v>22821400</v>
       </c>
       <c r="E41" s="3">
-        <v>24914300</v>
+        <v>25596900</v>
       </c>
       <c r="F41" s="3">
-        <v>5407200</v>
+        <v>5555400</v>
       </c>
       <c r="G41" s="3">
-        <v>6891300</v>
+        <v>7080200</v>
       </c>
       <c r="H41" s="3">
-        <v>4575700</v>
+        <v>4701000</v>
       </c>
       <c r="I41" s="3">
-        <v>4632000</v>
+        <v>4758900</v>
       </c>
       <c r="J41" s="3">
-        <v>4416400</v>
+        <v>4537400</v>
       </c>
       <c r="K41" s="3">
         <v>5463200</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>42070300</v>
+        <v>43222900</v>
       </c>
       <c r="E42" s="3">
-        <v>39988600</v>
+        <v>41084100</v>
       </c>
       <c r="F42" s="3">
-        <v>42907900</v>
+        <v>44083500</v>
       </c>
       <c r="G42" s="3">
-        <v>38641000</v>
+        <v>39699700</v>
       </c>
       <c r="H42" s="3">
-        <v>32361200</v>
+        <v>33247800</v>
       </c>
       <c r="I42" s="3">
-        <v>25877400</v>
+        <v>26586400</v>
       </c>
       <c r="J42" s="3">
-        <v>17364300</v>
+        <v>17840000</v>
       </c>
       <c r="K42" s="3">
         <v>12152400</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1310600</v>
+        <v>1346500</v>
       </c>
       <c r="E47" s="3">
-        <v>953100</v>
+        <v>979200</v>
       </c>
       <c r="F47" s="3">
-        <v>974700</v>
+        <v>1001400</v>
       </c>
       <c r="G47" s="3">
-        <v>725100</v>
+        <v>745000</v>
       </c>
       <c r="H47" s="3">
-        <v>588600</v>
+        <v>604800</v>
       </c>
       <c r="I47" s="3">
-        <v>263800</v>
+        <v>271100</v>
       </c>
       <c r="J47" s="3">
-        <v>304400</v>
+        <v>312800</v>
       </c>
       <c r="K47" s="3">
         <v>338000</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2664200</v>
+        <v>2737100</v>
       </c>
       <c r="E48" s="3">
-        <v>2577400</v>
+        <v>2648000</v>
       </c>
       <c r="F48" s="3">
-        <v>2601900</v>
+        <v>2673200</v>
       </c>
       <c r="G48" s="3">
-        <v>2682500</v>
+        <v>2756000</v>
       </c>
       <c r="H48" s="3">
-        <v>2660800</v>
+        <v>2733700</v>
       </c>
       <c r="I48" s="3">
-        <v>2058000</v>
+        <v>2114400</v>
       </c>
       <c r="J48" s="3">
-        <v>2079700</v>
+        <v>2136600</v>
       </c>
       <c r="K48" s="3">
         <v>2168700</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>727700</v>
+        <v>747600</v>
       </c>
       <c r="E49" s="3">
-        <v>619900</v>
+        <v>636800</v>
       </c>
       <c r="F49" s="3">
-        <v>573300</v>
+        <v>589000</v>
       </c>
       <c r="G49" s="3">
-        <v>578200</v>
+        <v>594100</v>
       </c>
       <c r="H49" s="3">
-        <v>616200</v>
+        <v>633100</v>
       </c>
       <c r="I49" s="3">
-        <v>428700</v>
+        <v>440400</v>
       </c>
       <c r="J49" s="3">
-        <v>378600</v>
+        <v>388900</v>
       </c>
       <c r="K49" s="3">
         <v>372500</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>258400</v>
+        <v>265500</v>
       </c>
       <c r="E52" s="3">
-        <v>322900</v>
+        <v>331800</v>
       </c>
       <c r="F52" s="3">
-        <v>57500</v>
+        <v>59100</v>
       </c>
       <c r="G52" s="3">
-        <v>81600</v>
+        <v>83800</v>
       </c>
       <c r="H52" s="3">
-        <v>38500</v>
+        <v>39500</v>
       </c>
       <c r="I52" s="3">
-        <v>104700</v>
+        <v>107500</v>
       </c>
       <c r="J52" s="3">
-        <v>240000</v>
+        <v>246600</v>
       </c>
       <c r="K52" s="3">
         <v>235100</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>363544000</v>
+        <v>373504000</v>
       </c>
       <c r="E54" s="3">
-        <v>350746000</v>
+        <v>360356000</v>
       </c>
       <c r="F54" s="3">
-        <v>326444000</v>
+        <v>335388000</v>
       </c>
       <c r="G54" s="3">
-        <v>291329000</v>
+        <v>299311000</v>
       </c>
       <c r="H54" s="3">
-        <v>264246000</v>
+        <v>271486000</v>
       </c>
       <c r="I54" s="3">
-        <v>248526000</v>
+        <v>255335000</v>
       </c>
       <c r="J54" s="3">
-        <v>230896000</v>
+        <v>237222000</v>
       </c>
       <c r="K54" s="3">
         <v>239226000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9097800</v>
+        <v>9347000</v>
       </c>
       <c r="E57" s="3">
-        <v>8363000</v>
+        <v>8592200</v>
       </c>
       <c r="F57" s="3">
-        <v>10555500</v>
+        <v>10844700</v>
       </c>
       <c r="G57" s="3">
-        <v>3648600</v>
+        <v>3748600</v>
       </c>
       <c r="H57" s="3">
-        <v>6239100</v>
+        <v>6410000</v>
       </c>
       <c r="I57" s="3">
-        <v>9549500</v>
+        <v>9811200</v>
       </c>
       <c r="J57" s="3">
-        <v>4812600</v>
+        <v>4944500</v>
       </c>
       <c r="K57" s="3">
         <v>11404000</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3243400</v>
+        <v>3332200</v>
       </c>
       <c r="E59" s="3">
-        <v>2965900</v>
+        <v>3047200</v>
       </c>
       <c r="F59" s="3">
-        <v>1938200</v>
+        <v>1991300</v>
       </c>
       <c r="G59" s="3">
-        <v>1766700</v>
+        <v>1815100</v>
       </c>
       <c r="H59" s="3">
-        <v>1970200</v>
+        <v>2024200</v>
       </c>
       <c r="I59" s="3">
-        <v>1729300</v>
+        <v>1776700</v>
       </c>
       <c r="J59" s="3">
-        <v>1666200</v>
+        <v>1711800</v>
       </c>
       <c r="K59" s="3">
         <v>1714900</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>51332300</v>
+        <v>52738700</v>
       </c>
       <c r="E61" s="3">
-        <v>51265600</v>
+        <v>52670100</v>
       </c>
       <c r="F61" s="3">
-        <v>50133100</v>
+        <v>51506600</v>
       </c>
       <c r="G61" s="3">
-        <v>42010900</v>
+        <v>43161900</v>
       </c>
       <c r="H61" s="3">
-        <v>36181800</v>
+        <v>37173100</v>
       </c>
       <c r="I61" s="3">
-        <v>32040700</v>
+        <v>32918500</v>
       </c>
       <c r="J61" s="3">
-        <v>30644900</v>
+        <v>31484500</v>
       </c>
       <c r="K61" s="3">
         <v>29549800</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>936800</v>
+        <v>962500</v>
       </c>
       <c r="E62" s="3">
-        <v>447400</v>
+        <v>459600</v>
       </c>
       <c r="F62" s="3">
-        <v>592100</v>
+        <v>608300</v>
       </c>
       <c r="G62" s="3">
-        <v>521300</v>
+        <v>535600</v>
       </c>
       <c r="H62" s="3">
-        <v>489700</v>
+        <v>503100</v>
       </c>
       <c r="I62" s="3">
-        <v>399100</v>
+        <v>410000</v>
       </c>
       <c r="J62" s="3">
-        <v>347800</v>
+        <v>357300</v>
       </c>
       <c r="K62" s="3">
         <v>396700</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>340427000</v>
+        <v>349754000</v>
       </c>
       <c r="E66" s="3">
-        <v>329750000</v>
+        <v>338784000</v>
       </c>
       <c r="F66" s="3">
-        <v>307580000</v>
+        <v>316006000</v>
       </c>
       <c r="G66" s="3">
-        <v>274500000</v>
+        <v>282021000</v>
       </c>
       <c r="H66" s="3">
-        <v>248543000</v>
+        <v>255353000</v>
       </c>
       <c r="I66" s="3">
-        <v>232656000</v>
+        <v>239030000</v>
       </c>
       <c r="J66" s="3">
-        <v>216029000</v>
+        <v>221947000</v>
       </c>
       <c r="K66" s="3">
         <v>223528000</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>18240100</v>
+        <v>18739900</v>
       </c>
       <c r="E72" s="3">
-        <v>17337600</v>
+        <v>17812600</v>
       </c>
       <c r="F72" s="3">
-        <v>15616600</v>
+        <v>16044400</v>
       </c>
       <c r="G72" s="3">
-        <v>14065800</v>
+        <v>14451200</v>
       </c>
       <c r="H72" s="3">
-        <v>13522900</v>
+        <v>13893400</v>
       </c>
       <c r="I72" s="3">
-        <v>12501000</v>
+        <v>12843500</v>
       </c>
       <c r="J72" s="3">
-        <v>11402600</v>
+        <v>11715000</v>
       </c>
       <c r="K72" s="3">
         <v>11250900</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>23116800</v>
+        <v>23750200</v>
       </c>
       <c r="E76" s="3">
-        <v>20996200</v>
+        <v>21571400</v>
       </c>
       <c r="F76" s="3">
-        <v>18864700</v>
+        <v>19381500</v>
       </c>
       <c r="G76" s="3">
-        <v>16829100</v>
+        <v>17290200</v>
       </c>
       <c r="H76" s="3">
-        <v>15702600</v>
+        <v>16132800</v>
       </c>
       <c r="I76" s="3">
-        <v>15870100</v>
+        <v>16304900</v>
       </c>
       <c r="J76" s="3">
-        <v>14867100</v>
+        <v>15274400</v>
       </c>
       <c r="K76" s="3">
         <v>15697300</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1733900</v>
+        <v>1781400</v>
       </c>
       <c r="E81" s="3">
-        <v>2226400</v>
+        <v>2287400</v>
       </c>
       <c r="F81" s="3">
-        <v>1840800</v>
+        <v>1891300</v>
       </c>
       <c r="G81" s="3">
-        <v>918600</v>
+        <v>943800</v>
       </c>
       <c r="H81" s="3">
-        <v>1363500</v>
+        <v>1400900</v>
       </c>
       <c r="I81" s="3">
-        <v>1373900</v>
+        <v>1411500</v>
       </c>
       <c r="J81" s="3">
-        <v>981900</v>
+        <v>1008800</v>
       </c>
       <c r="K81" s="3">
         <v>812200</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>725000</v>
+        <v>744900</v>
       </c>
       <c r="E83" s="3">
-        <v>678400</v>
+        <v>697000</v>
       </c>
       <c r="F83" s="3">
-        <v>578100</v>
+        <v>593900</v>
       </c>
       <c r="G83" s="3">
-        <v>391000</v>
+        <v>401700</v>
       </c>
       <c r="H83" s="3">
-        <v>369200</v>
+        <v>379300</v>
       </c>
       <c r="I83" s="3">
-        <v>199000</v>
+        <v>204400</v>
       </c>
       <c r="J83" s="3">
-        <v>172100</v>
+        <v>176800</v>
       </c>
       <c r="K83" s="3">
         <v>194100</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1184000</v>
+        <v>1216500</v>
       </c>
       <c r="E89" s="3">
-        <v>13595600</v>
+        <v>13968100</v>
       </c>
       <c r="F89" s="3">
-        <v>2773800</v>
+        <v>2849800</v>
       </c>
       <c r="G89" s="3">
-        <v>2632400</v>
+        <v>2704500</v>
       </c>
       <c r="H89" s="3">
-        <v>1365400</v>
+        <v>1402800</v>
       </c>
       <c r="I89" s="3">
-        <v>6686900</v>
+        <v>6870100</v>
       </c>
       <c r="J89" s="3">
-        <v>-1444700</v>
+        <v>-1484300</v>
       </c>
       <c r="K89" s="3">
         <v>3777100</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-120200</v>
+        <v>-123500</v>
       </c>
       <c r="E91" s="3">
-        <v>-126200</v>
+        <v>-129700</v>
       </c>
       <c r="F91" s="3">
-        <v>-87100</v>
+        <v>-89400</v>
       </c>
       <c r="G91" s="3">
-        <v>-109000</v>
+        <v>-112000</v>
       </c>
       <c r="H91" s="3">
-        <v>-313600</v>
+        <v>-322200</v>
       </c>
       <c r="I91" s="3">
-        <v>-86600</v>
+        <v>-89000</v>
       </c>
       <c r="J91" s="3">
-        <v>-118400</v>
+        <v>-121700</v>
       </c>
       <c r="K91" s="3">
         <v>-100900</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1645500</v>
+        <v>-1690600</v>
       </c>
       <c r="E94" s="3">
-        <v>-5087100</v>
+        <v>-5226500</v>
       </c>
       <c r="F94" s="3">
-        <v>-7786800</v>
+        <v>-8000100</v>
       </c>
       <c r="G94" s="3">
-        <v>-1063200</v>
+        <v>-1092300</v>
       </c>
       <c r="H94" s="3">
-        <v>-6269300</v>
+        <v>-6441100</v>
       </c>
       <c r="I94" s="3">
-        <v>-8082000</v>
+        <v>-8303400</v>
       </c>
       <c r="J94" s="3">
-        <v>1375100</v>
+        <v>1412800</v>
       </c>
       <c r="K94" s="3">
         <v>-3253700</v>
@@ -4227,19 +4227,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-714200</v>
+        <v>-733800</v>
       </c>
       <c r="E96" s="3">
-        <v>-478100</v>
+        <v>-491200</v>
       </c>
       <c r="F96" s="3">
-        <v>-268900</v>
+        <v>-276300</v>
       </c>
       <c r="G96" s="3">
-        <v>-369100</v>
+        <v>-379200</v>
       </c>
       <c r="H96" s="3">
-        <v>-319500</v>
+        <v>-328200</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2087900</v>
+        <v>-2145100</v>
       </c>
       <c r="E100" s="3">
-        <v>1401400</v>
+        <v>1439800</v>
       </c>
       <c r="F100" s="3">
-        <v>6625300</v>
+        <v>6806800</v>
       </c>
       <c r="G100" s="3">
-        <v>1728100</v>
+        <v>1775400</v>
       </c>
       <c r="H100" s="3">
-        <v>4504800</v>
+        <v>4628300</v>
       </c>
       <c r="I100" s="3">
-        <v>1107200</v>
+        <v>1137600</v>
       </c>
       <c r="J100" s="3">
-        <v>-44600</v>
+        <v>-45800</v>
       </c>
       <c r="K100" s="3">
         <v>256500</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-124200</v>
+        <v>-127600</v>
       </c>
       <c r="E101" s="3">
-        <v>22500</v>
+        <v>23100</v>
       </c>
       <c r="F101" s="3">
-        <v>774700</v>
+        <v>795900</v>
       </c>
       <c r="G101" s="3">
-        <v>-670400</v>
+        <v>-688800</v>
       </c>
       <c r="H101" s="3">
-        <v>139800</v>
+        <v>143600</v>
       </c>
       <c r="I101" s="3">
-        <v>170800</v>
+        <v>175400</v>
       </c>
       <c r="J101" s="3">
-        <v>-384500</v>
+        <v>-395000</v>
       </c>
       <c r="K101" s="3">
         <v>-50400</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2673600</v>
+        <v>-2746900</v>
       </c>
       <c r="E102" s="3">
-        <v>9932400</v>
+        <v>10204600</v>
       </c>
       <c r="F102" s="3">
-        <v>2387000</v>
+        <v>2452400</v>
       </c>
       <c r="G102" s="3">
-        <v>2626800</v>
+        <v>2698800</v>
       </c>
       <c r="H102" s="3">
-        <v>-259400</v>
+        <v>-266500</v>
       </c>
       <c r="I102" s="3">
-        <v>-117100</v>
+        <v>-120300</v>
       </c>
       <c r="J102" s="3">
-        <v>-498600</v>
+        <v>-512300</v>
       </c>
       <c r="K102" s="3">
         <v>729400</v>

--- a/AAII_Financials/Yearly/WF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WF_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>WF</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>15481200</v>
+        <v>7325300</v>
       </c>
       <c r="E8" s="3">
-        <v>10990900</v>
+        <v>7969300</v>
       </c>
       <c r="F8" s="3">
-        <v>7421100</v>
+        <v>7398600</v>
       </c>
       <c r="G8" s="3">
-        <v>7142900</v>
+        <v>6310500</v>
       </c>
       <c r="H8" s="3">
-        <v>7932600</v>
+        <v>5947900</v>
       </c>
       <c r="I8" s="3">
-        <v>7263400</v>
+        <v>6157300</v>
       </c>
       <c r="J8" s="3">
-        <v>6413000</v>
+        <v>5349900</v>
       </c>
       <c r="K8" s="3">
         <v>6554500</v>
@@ -770,26 +770,26 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>30300</v>
+      </c>
+      <c r="F9" s="3">
+        <v>27200</v>
+      </c>
+      <c r="G9" s="3">
+        <v>26300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>25200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>24800</v>
+      </c>
+      <c r="J9" s="3">
+        <v>24300</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -815,26 +815,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>7294700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7939000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>7371400</v>
+      </c>
+      <c r="G10" s="3">
+        <v>6284200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>5922800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>6132500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5325600</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>40700</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>64100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>152200</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>24400</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-381300</v>
+        <v>542600</v>
       </c>
       <c r="E15" s="3">
-        <v>-394300</v>
+        <v>492600</v>
       </c>
       <c r="F15" s="3">
-        <v>-395200</v>
+        <v>396800</v>
       </c>
       <c r="G15" s="3">
-        <v>-392700</v>
+        <v>208800</v>
       </c>
       <c r="H15" s="3">
-        <v>-362600</v>
+        <v>183300</v>
       </c>
       <c r="I15" s="3">
-        <v>-165600</v>
+        <v>190900</v>
       </c>
       <c r="J15" s="3">
-        <v>-140600</v>
+        <v>184400</v>
       </c>
       <c r="K15" s="3">
         <v>-194100</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10345400</v>
+        <v>4599300</v>
       </c>
       <c r="E17" s="3">
-        <v>5132400</v>
+        <v>4406900</v>
       </c>
       <c r="F17" s="3">
-        <v>2599900</v>
+        <v>4226800</v>
       </c>
       <c r="G17" s="3">
-        <v>3238600</v>
+        <v>4389200</v>
       </c>
       <c r="H17" s="3">
-        <v>3793000</v>
+        <v>3524200</v>
       </c>
       <c r="I17" s="3">
-        <v>3339400</v>
+        <v>3609800</v>
       </c>
       <c r="J17" s="3">
-        <v>3144200</v>
+        <v>3334500</v>
       </c>
       <c r="K17" s="3">
         <v>3375300</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>5135700</v>
+        <v>2726000</v>
       </c>
       <c r="E18" s="3">
-        <v>5858500</v>
+        <v>3562400</v>
       </c>
       <c r="F18" s="3">
-        <v>4821100</v>
+        <v>3171800</v>
       </c>
       <c r="G18" s="3">
-        <v>3904300</v>
+        <v>1921300</v>
       </c>
       <c r="H18" s="3">
-        <v>4139600</v>
+        <v>2423700</v>
       </c>
       <c r="I18" s="3">
-        <v>3923900</v>
+        <v>2547500</v>
       </c>
       <c r="J18" s="3">
-        <v>3268800</v>
+        <v>2015400</v>
       </c>
       <c r="K18" s="3">
         <v>3179200</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2497600</v>
+        <v>-27200</v>
       </c>
       <c r="E20" s="3">
-        <v>-2494400</v>
+        <v>-32200</v>
       </c>
       <c r="F20" s="3">
-        <v>-2009200</v>
+        <v>-39900</v>
       </c>
       <c r="G20" s="3">
-        <v>-2403300</v>
+        <v>-69800</v>
       </c>
       <c r="H20" s="3">
-        <v>-2097300</v>
+        <v>40700</v>
       </c>
       <c r="I20" s="3">
-        <v>-1820300</v>
+        <v>28600</v>
       </c>
       <c r="J20" s="3">
-        <v>-1806700</v>
+        <v>190700</v>
       </c>
       <c r="K20" s="3">
         <v>-1983100</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3383000</v>
+        <v>3295800</v>
       </c>
       <c r="E21" s="3">
-        <v>4061000</v>
+        <v>4087100</v>
       </c>
       <c r="F21" s="3">
-        <v>3405900</v>
+        <v>3608500</v>
       </c>
       <c r="G21" s="3">
-        <v>1902600</v>
+        <v>2199900</v>
       </c>
       <c r="H21" s="3">
-        <v>2421600</v>
+        <v>2566300</v>
       </c>
       <c r="I21" s="3">
-        <v>2308100</v>
+        <v>2709800</v>
       </c>
       <c r="J21" s="3">
-        <v>1639000</v>
+        <v>2009100</v>
       </c>
       <c r="K21" s="3">
         <v>1390200</v>
@@ -1274,26 +1274,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2638100</v>
+        <v>2712500</v>
       </c>
       <c r="E23" s="3">
-        <v>3364000</v>
+        <v>3566600</v>
       </c>
       <c r="F23" s="3">
-        <v>2811900</v>
+        <v>3147600</v>
       </c>
       <c r="G23" s="3">
-        <v>1500900</v>
+        <v>1838900</v>
       </c>
       <c r="H23" s="3">
-        <v>2042300</v>
+        <v>2358700</v>
       </c>
       <c r="I23" s="3">
-        <v>2103700</v>
+        <v>2519500</v>
       </c>
       <c r="J23" s="3">
-        <v>1462100</v>
+        <v>1824900</v>
       </c>
       <c r="K23" s="3">
         <v>1196100</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>667900</v>
+        <v>686800</v>
       </c>
       <c r="E24" s="3">
-        <v>871000</v>
+        <v>923500</v>
       </c>
       <c r="F24" s="3">
-        <v>706400</v>
+        <v>790700</v>
       </c>
       <c r="G24" s="3">
-        <v>364500</v>
+        <v>446600</v>
       </c>
       <c r="H24" s="3">
-        <v>514100</v>
+        <v>593700</v>
       </c>
       <c r="I24" s="3">
-        <v>564900</v>
+        <v>676600</v>
       </c>
       <c r="J24" s="3">
-        <v>314600</v>
+        <v>392600</v>
       </c>
       <c r="K24" s="3">
         <v>212400</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1970200</v>
+        <v>2025700</v>
       </c>
       <c r="E26" s="3">
-        <v>2493000</v>
+        <v>2643100</v>
       </c>
       <c r="F26" s="3">
-        <v>2105500</v>
+        <v>2356800</v>
       </c>
       <c r="G26" s="3">
-        <v>1136400</v>
+        <v>1392300</v>
       </c>
       <c r="H26" s="3">
-        <v>1528200</v>
+        <v>1764900</v>
       </c>
       <c r="I26" s="3">
-        <v>1538700</v>
+        <v>1842900</v>
       </c>
       <c r="J26" s="3">
-        <v>1147600</v>
+        <v>1432300</v>
       </c>
       <c r="K26" s="3">
         <v>983700</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1781400</v>
+        <v>1831600</v>
       </c>
       <c r="E27" s="3">
-        <v>2287400</v>
+        <v>2425200</v>
       </c>
       <c r="F27" s="3">
-        <v>1891300</v>
+        <v>2117000</v>
       </c>
       <c r="G27" s="3">
-        <v>943800</v>
+        <v>1156300</v>
       </c>
       <c r="H27" s="3">
-        <v>1400900</v>
+        <v>1617900</v>
       </c>
       <c r="I27" s="3">
-        <v>1411500</v>
+        <v>1690500</v>
       </c>
       <c r="J27" s="3">
-        <v>1008800</v>
+        <v>1259100</v>
       </c>
       <c r="K27" s="3">
         <v>812200</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2497600</v>
+        <v>27200</v>
       </c>
       <c r="E32" s="3">
-        <v>2494400</v>
+        <v>32200</v>
       </c>
       <c r="F32" s="3">
-        <v>2009200</v>
+        <v>39900</v>
       </c>
       <c r="G32" s="3">
-        <v>2403300</v>
+        <v>69800</v>
       </c>
       <c r="H32" s="3">
-        <v>2097300</v>
+        <v>-40700</v>
       </c>
       <c r="I32" s="3">
-        <v>1820300</v>
+        <v>-28600</v>
       </c>
       <c r="J32" s="3">
-        <v>1806700</v>
+        <v>-190700</v>
       </c>
       <c r="K32" s="3">
         <v>1983100</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1781400</v>
+        <v>1932700</v>
       </c>
       <c r="E33" s="3">
-        <v>2287400</v>
+        <v>2498100</v>
       </c>
       <c r="F33" s="3">
-        <v>1891300</v>
+        <v>2172600</v>
       </c>
       <c r="G33" s="3">
-        <v>943800</v>
+        <v>1201200</v>
       </c>
       <c r="H33" s="3">
-        <v>1400900</v>
+        <v>1621700</v>
       </c>
       <c r="I33" s="3">
-        <v>1411500</v>
+        <v>1826300</v>
       </c>
       <c r="J33" s="3">
-        <v>1008800</v>
+        <v>1415500</v>
       </c>
       <c r="K33" s="3">
         <v>812200</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1781400</v>
+        <v>1932700</v>
       </c>
       <c r="E35" s="3">
-        <v>2287400</v>
+        <v>2498100</v>
       </c>
       <c r="F35" s="3">
-        <v>1891300</v>
+        <v>2172600</v>
       </c>
       <c r="G35" s="3">
-        <v>943800</v>
+        <v>1201200</v>
       </c>
       <c r="H35" s="3">
-        <v>1400900</v>
+        <v>1621700</v>
       </c>
       <c r="I35" s="3">
-        <v>1411500</v>
+        <v>1826300</v>
       </c>
       <c r="J35" s="3">
-        <v>1008800</v>
+        <v>1415500</v>
       </c>
       <c r="K35" s="3">
         <v>812200</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>22821400</v>
+        <v>12476200</v>
       </c>
       <c r="E41" s="3">
-        <v>25596900</v>
+        <v>8948700</v>
       </c>
       <c r="F41" s="3">
-        <v>5555400</v>
+        <v>6351600</v>
       </c>
       <c r="G41" s="3">
-        <v>7080200</v>
+        <v>9180600</v>
       </c>
       <c r="H41" s="3">
-        <v>4701000</v>
+        <v>5537100</v>
       </c>
       <c r="I41" s="3">
-        <v>4758900</v>
+        <v>6061400</v>
       </c>
       <c r="J41" s="3">
-        <v>4537400</v>
+        <v>6466900</v>
       </c>
       <c r="K41" s="3">
         <v>5463200</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>43222900</v>
+        <v>18215800</v>
       </c>
       <c r="E42" s="3">
-        <v>41084100</v>
+        <v>20372700</v>
       </c>
       <c r="F42" s="3">
-        <v>44083500</v>
+        <v>19260200</v>
       </c>
       <c r="G42" s="3">
-        <v>39699700</v>
+        <v>22333400</v>
       </c>
       <c r="H42" s="3">
-        <v>33247800</v>
+        <v>14518100</v>
       </c>
       <c r="I42" s="3">
-        <v>26586400</v>
+        <v>16046500</v>
       </c>
       <c r="J42" s="3">
-        <v>17840000</v>
+        <v>21286100</v>
       </c>
       <c r="K42" s="3">
         <v>12152400</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>8598900</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>6635000</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>7736000</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>6759600</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>8043900</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>7755700</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>6861800</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2127,26 +2127,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>3229200</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>2949300</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>2520900</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>2451500</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>2131900</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>1820100</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>1945100</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>53874000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>57522300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>47485200</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>46872600</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>39901000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>41740500</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>42529600</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1346500</v>
+        <v>33116700</v>
       </c>
       <c r="E47" s="3">
-        <v>979200</v>
+        <v>33811000</v>
       </c>
       <c r="F47" s="3">
-        <v>1001400</v>
+        <v>37460700</v>
       </c>
       <c r="G47" s="3">
-        <v>745000</v>
+        <v>34932400</v>
       </c>
       <c r="H47" s="3">
-        <v>604800</v>
+        <v>32351800</v>
       </c>
       <c r="I47" s="3">
-        <v>271100</v>
+        <v>28724300</v>
       </c>
       <c r="J47" s="3">
-        <v>312800</v>
+        <v>28818200</v>
       </c>
       <c r="K47" s="3">
         <v>338000</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2737100</v>
+        <v>4983700</v>
       </c>
       <c r="E48" s="3">
-        <v>2648000</v>
+        <v>4559000</v>
       </c>
       <c r="F48" s="3">
-        <v>2673200</v>
+        <v>4158200</v>
       </c>
       <c r="G48" s="3">
-        <v>2756000</v>
+        <v>4046000</v>
       </c>
       <c r="H48" s="3">
-        <v>2733700</v>
+        <v>2914500</v>
       </c>
       <c r="I48" s="3">
-        <v>2114400</v>
+        <v>2201200</v>
       </c>
       <c r="J48" s="3">
-        <v>2136600</v>
+        <v>2319200</v>
       </c>
       <c r="K48" s="3">
         <v>2168700</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>747600</v>
+        <v>582000</v>
       </c>
       <c r="E49" s="3">
-        <v>636800</v>
+        <v>506100</v>
       </c>
       <c r="F49" s="3">
-        <v>589000</v>
+        <v>485000</v>
       </c>
       <c r="G49" s="3">
-        <v>594100</v>
+        <v>535900</v>
       </c>
       <c r="H49" s="3">
-        <v>633100</v>
+        <v>536100</v>
       </c>
       <c r="I49" s="3">
-        <v>440400</v>
+        <v>320900</v>
       </c>
       <c r="J49" s="3">
-        <v>388900</v>
+        <v>269700</v>
       </c>
       <c r="K49" s="3">
         <v>372500</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>265500</v>
+        <v>17293300</v>
       </c>
       <c r="E52" s="3">
-        <v>331800</v>
+        <v>17375400</v>
       </c>
       <c r="F52" s="3">
-        <v>59100</v>
+        <v>11554700</v>
       </c>
       <c r="G52" s="3">
-        <v>83800</v>
+        <v>11178600</v>
       </c>
       <c r="H52" s="3">
-        <v>39500</v>
+        <v>10625300</v>
       </c>
       <c r="I52" s="3">
-        <v>107500</v>
+        <v>8782100</v>
       </c>
       <c r="J52" s="3">
-        <v>246600</v>
+        <v>2000500</v>
       </c>
       <c r="K52" s="3">
         <v>235100</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>373504000</v>
+        <v>384037900</v>
       </c>
       <c r="E54" s="3">
-        <v>360356000</v>
+        <v>382053600</v>
       </c>
       <c r="F54" s="3">
-        <v>335388000</v>
+        <v>375418800</v>
       </c>
       <c r="G54" s="3">
-        <v>299311000</v>
+        <v>366711400</v>
       </c>
       <c r="H54" s="3">
-        <v>271486000</v>
+        <v>313541700</v>
       </c>
       <c r="I54" s="3">
-        <v>255335000</v>
+        <v>305813800</v>
       </c>
       <c r="J54" s="3">
-        <v>237222000</v>
+        <v>296084700</v>
       </c>
       <c r="K54" s="3">
         <v>239226000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9347000</v>
+        <v>283746600</v>
       </c>
       <c r="E57" s="3">
-        <v>8592200</v>
+        <v>276784200</v>
       </c>
       <c r="F57" s="3">
-        <v>10844700</v>
+        <v>272720500</v>
       </c>
       <c r="G57" s="3">
-        <v>3748600</v>
+        <v>271530900</v>
       </c>
       <c r="H57" s="3">
-        <v>6410000</v>
+        <v>229266200</v>
       </c>
       <c r="I57" s="3">
-        <v>9811200</v>
+        <v>223391800</v>
       </c>
       <c r="J57" s="3">
-        <v>4944500</v>
+        <v>219698500</v>
       </c>
       <c r="K57" s="3">
         <v>11404000</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>9863100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>10474200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>7069700</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>9567700</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>2684200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>2072300</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3162100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3332200</v>
+        <v>795100</v>
       </c>
       <c r="E59" s="3">
-        <v>3047200</v>
+        <v>1352700</v>
       </c>
       <c r="F59" s="3">
-        <v>1991300</v>
+        <v>1201900</v>
       </c>
       <c r="G59" s="3">
-        <v>1815100</v>
+        <v>1111100</v>
       </c>
       <c r="H59" s="3">
-        <v>2024200</v>
+        <v>182100</v>
       </c>
       <c r="I59" s="3">
-        <v>1776700</v>
+        <v>167200</v>
       </c>
       <c r="J59" s="3">
-        <v>1711800</v>
+        <v>242000</v>
       </c>
       <c r="K59" s="3">
         <v>1714900</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>297751000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>291171000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>282730500</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>284092800</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>232132500</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>225675500</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>223140500</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>52738700</v>
+        <v>54929200</v>
       </c>
       <c r="E61" s="3">
-        <v>52670100</v>
+        <v>57545700</v>
       </c>
       <c r="F61" s="3">
-        <v>51506600</v>
+        <v>58157500</v>
       </c>
       <c r="G61" s="3">
-        <v>43161900</v>
+        <v>53326300</v>
       </c>
       <c r="H61" s="3">
-        <v>37173100</v>
+        <v>43408600</v>
       </c>
       <c r="I61" s="3">
-        <v>32918500</v>
+        <v>40367300</v>
       </c>
       <c r="J61" s="3">
-        <v>31484500</v>
+        <v>40014700</v>
       </c>
       <c r="K61" s="3">
         <v>29549800</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>962500</v>
+        <v>4724200</v>
       </c>
       <c r="E62" s="3">
-        <v>459600</v>
+        <v>7685200</v>
       </c>
       <c r="F62" s="3">
-        <v>608300</v>
+        <v>9505400</v>
       </c>
       <c r="G62" s="3">
-        <v>535600</v>
+        <v>3876200</v>
       </c>
       <c r="H62" s="3">
-        <v>503100</v>
+        <v>15528400</v>
       </c>
       <c r="I62" s="3">
-        <v>410000</v>
+        <v>19696100</v>
       </c>
       <c r="J62" s="3">
-        <v>357300</v>
+        <v>13447900</v>
       </c>
       <c r="K62" s="3">
         <v>396700</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>349754000</v>
+        <v>358283300</v>
       </c>
       <c r="E66" s="3">
-        <v>338784000</v>
+        <v>356904800</v>
       </c>
       <c r="F66" s="3">
-        <v>316006000</v>
+        <v>351198600</v>
       </c>
       <c r="G66" s="3">
-        <v>282021000</v>
+        <v>342153300</v>
       </c>
       <c r="H66" s="3">
-        <v>255353000</v>
+        <v>291460600</v>
       </c>
       <c r="I66" s="3">
-        <v>239030000</v>
+        <v>286094000</v>
       </c>
       <c r="J66" s="3">
-        <v>221947000</v>
+        <v>276833900</v>
       </c>
       <c r="K66" s="3">
         <v>223528000</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>18739900</v>
+        <v>19268400</v>
       </c>
       <c r="E72" s="3">
-        <v>17812600</v>
+        <v>18885100</v>
       </c>
       <c r="F72" s="3">
-        <v>16044400</v>
+        <v>17959400</v>
       </c>
       <c r="G72" s="3">
-        <v>14451200</v>
+        <v>17705400</v>
       </c>
       <c r="H72" s="3">
-        <v>13893400</v>
+        <v>16045600</v>
       </c>
       <c r="I72" s="3">
-        <v>12843500</v>
+        <v>15382600</v>
       </c>
       <c r="J72" s="3">
-        <v>11715000</v>
+        <v>14621900</v>
       </c>
       <c r="K72" s="3">
         <v>11250900</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>23750200</v>
+        <v>24420000</v>
       </c>
       <c r="E76" s="3">
-        <v>21571400</v>
+        <v>22870300</v>
       </c>
       <c r="F76" s="3">
-        <v>19381500</v>
+        <v>21694800</v>
       </c>
       <c r="G76" s="3">
-        <v>17290200</v>
+        <v>21183700</v>
       </c>
       <c r="H76" s="3">
-        <v>16132800</v>
+        <v>18631900</v>
       </c>
       <c r="I76" s="3">
-        <v>16304900</v>
+        <v>19528300</v>
       </c>
       <c r="J76" s="3">
-        <v>15274400</v>
+        <v>19064500</v>
       </c>
       <c r="K76" s="3">
         <v>15697300</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1781400</v>
+        <v>1932700</v>
       </c>
       <c r="E81" s="3">
-        <v>2287400</v>
+        <v>2498100</v>
       </c>
       <c r="F81" s="3">
-        <v>1891300</v>
+        <v>2172600</v>
       </c>
       <c r="G81" s="3">
-        <v>943800</v>
+        <v>1201200</v>
       </c>
       <c r="H81" s="3">
-        <v>1400900</v>
+        <v>1621700</v>
       </c>
       <c r="I81" s="3">
-        <v>1411500</v>
+        <v>1826300</v>
       </c>
       <c r="J81" s="3">
-        <v>1008800</v>
+        <v>1415500</v>
       </c>
       <c r="K81" s="3">
         <v>812200</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>744900</v>
+        <v>641800</v>
       </c>
       <c r="E83" s="3">
-        <v>697000</v>
+        <v>609500</v>
       </c>
       <c r="F83" s="3">
-        <v>593900</v>
+        <v>539500</v>
       </c>
       <c r="G83" s="3">
-        <v>401700</v>
+        <v>366500</v>
       </c>
       <c r="H83" s="3">
-        <v>379300</v>
+        <v>326800</v>
       </c>
       <c r="I83" s="3">
-        <v>204400</v>
+        <v>124300</v>
       </c>
       <c r="J83" s="3">
-        <v>176800</v>
+        <v>127300</v>
       </c>
       <c r="K83" s="3">
         <v>194100</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1216500</v>
+        <v>-10452600</v>
       </c>
       <c r="E89" s="3">
-        <v>13968100</v>
+        <v>-3905800</v>
       </c>
       <c r="F89" s="3">
-        <v>2849800</v>
+        <v>-16816200</v>
       </c>
       <c r="G89" s="3">
-        <v>2704500</v>
+        <v>-21844000</v>
       </c>
       <c r="H89" s="3">
-        <v>1402800</v>
+        <v>-11725400</v>
       </c>
       <c r="I89" s="3">
-        <v>6870100</v>
+        <v>-4343700</v>
       </c>
       <c r="J89" s="3">
-        <v>-1484300</v>
+        <v>-14616200</v>
       </c>
       <c r="K89" s="3">
         <v>3777100</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-123500</v>
+        <v>-127000</v>
       </c>
       <c r="E91" s="3">
-        <v>-129700</v>
+        <v>-137500</v>
       </c>
       <c r="F91" s="3">
-        <v>-89400</v>
+        <v>-100100</v>
       </c>
       <c r="G91" s="3">
-        <v>-112000</v>
+        <v>-137200</v>
       </c>
       <c r="H91" s="3">
-        <v>-322200</v>
+        <v>-372100</v>
       </c>
       <c r="I91" s="3">
-        <v>-89000</v>
+        <v>-106600</v>
       </c>
       <c r="J91" s="3">
-        <v>-121700</v>
+        <v>-151900</v>
       </c>
       <c r="K91" s="3">
         <v>-100900</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1690600</v>
+        <v>-1738300</v>
       </c>
       <c r="E94" s="3">
-        <v>-5226500</v>
+        <v>-5541200</v>
       </c>
       <c r="F94" s="3">
-        <v>-8000100</v>
+        <v>-8955000</v>
       </c>
       <c r="G94" s="3">
-        <v>-1092300</v>
+        <v>-1338300</v>
       </c>
       <c r="H94" s="3">
-        <v>-6441100</v>
+        <v>-7438900</v>
       </c>
       <c r="I94" s="3">
-        <v>-8303400</v>
+        <v>-9944900</v>
       </c>
       <c r="J94" s="3">
-        <v>1412800</v>
+        <v>1763300</v>
       </c>
       <c r="K94" s="3">
         <v>-3253700</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-733800</v>
+        <v>855600</v>
       </c>
       <c r="E96" s="3">
-        <v>-491200</v>
+        <v>593800</v>
       </c>
       <c r="F96" s="3">
-        <v>-276300</v>
+        <v>364900</v>
       </c>
       <c r="G96" s="3">
-        <v>-379200</v>
+        <v>509500</v>
       </c>
       <c r="H96" s="3">
-        <v>-328200</v>
+        <v>518600</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>435000</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>481500</v>
       </c>
       <c r="K96" s="3">
         <v>-129600</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2145100</v>
+        <v>9497700</v>
       </c>
       <c r="E100" s="3">
-        <v>1439800</v>
+        <v>20241500</v>
       </c>
       <c r="F100" s="3">
-        <v>6806800</v>
+        <v>27625300</v>
       </c>
       <c r="G100" s="3">
-        <v>1775400</v>
+        <v>27332800</v>
       </c>
       <c r="H100" s="3">
-        <v>4628300</v>
+        <v>18690700</v>
       </c>
       <c r="I100" s="3">
-        <v>1137600</v>
+        <v>13934400</v>
       </c>
       <c r="J100" s="3">
-        <v>-45800</v>
+        <v>12706400</v>
       </c>
       <c r="K100" s="3">
         <v>256500</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-127600</v>
+        <v>-131200</v>
       </c>
       <c r="E101" s="3">
-        <v>23100</v>
+        <v>24500</v>
       </c>
       <c r="F101" s="3">
-        <v>795900</v>
+        <v>890900</v>
       </c>
       <c r="G101" s="3">
-        <v>-688800</v>
+        <v>-843900</v>
       </c>
       <c r="H101" s="3">
-        <v>143600</v>
+        <v>165800</v>
       </c>
       <c r="I101" s="3">
-        <v>175400</v>
+        <v>210100</v>
       </c>
       <c r="J101" s="3">
-        <v>-395000</v>
+        <v>-493000</v>
       </c>
       <c r="K101" s="3">
         <v>-50400</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2746900</v>
+        <v>-2824400</v>
       </c>
       <c r="E102" s="3">
-        <v>10204600</v>
+        <v>10819000</v>
       </c>
       <c r="F102" s="3">
-        <v>2452400</v>
+        <v>2745100</v>
       </c>
       <c r="G102" s="3">
-        <v>2698800</v>
+        <v>3306500</v>
       </c>
       <c r="H102" s="3">
-        <v>-266500</v>
+        <v>-307800</v>
       </c>
       <c r="I102" s="3">
-        <v>-120300</v>
+        <v>-144100</v>
       </c>
       <c r="J102" s="3">
-        <v>-512300</v>
+        <v>-639400</v>
       </c>
       <c r="K102" s="3">
         <v>729400</v>

--- a/AAII_Financials/Yearly/WF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WF_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>WF</t>
   </si>
@@ -656,144 +656,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7762200</v>
+      </c>
+      <c r="E8" s="3">
         <v>7325300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7969300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7398600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6310500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5947900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6157300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5349900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6554500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6436700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7461100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8639000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9148600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9763900</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E9" s="3">
         <v>30600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>30300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>27200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>26300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>25200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>24800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>24300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
@@ -809,36 +815,39 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7735500</v>
+      </c>
+      <c r="E10" s="3">
         <v>7294700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7939000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7371400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6284200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5922800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6132500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5325600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -854,9 +863,12 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,36 +979,39 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E14" s="3">
         <v>40700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>28000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>64100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>152200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>24400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1008,54 +1027,60 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>572100</v>
+      </c>
+      <c r="E15" s="3">
         <v>542600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>492600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>396800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>208800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>183300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>190900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>184400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-194100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-178200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-184600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-215000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-187500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-177900</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4865500</v>
+      </c>
+      <c r="E17" s="3">
         <v>4599300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4406900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4226800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4389200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3524200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3609800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3334500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3375300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3735900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4725900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6553500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6595600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7124100</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2896700</v>
+      </c>
+      <c r="E18" s="3">
         <v>2726000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3562400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3171800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1921300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2423700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2547500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2015400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3179200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2700800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2735200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2085400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2553000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2639700</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,98 +1211,105 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-27200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-32200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-39900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-69800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>40700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>28600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>190700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1983100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1626400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2059400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1823700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1177200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-578900</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3452300</v>
+      </c>
+      <c r="E21" s="3">
         <v>3295800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4087100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3608500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2199900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2566300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2709800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2009100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1390200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1250200</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3">
         <v>532200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1623200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2301600</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1295,8 +1334,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1313,99 +1352,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2858600</v>
+      </c>
+      <c r="E23" s="3">
         <v>2712500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3566600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3147600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1838900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2358700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2519500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1824900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1196100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1074400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>675900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>261800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1375900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2060800</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>711700</v>
+      </c>
+      <c r="E24" s="3">
         <v>686800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>923500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>790700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>446600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>593700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>676600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>392600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>212400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>278600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>233400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>31900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>299700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>491900</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2146900</v>
+      </c>
+      <c r="E26" s="3">
         <v>2025700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2643100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2356800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1392300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1764900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1842900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1432300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>983700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>795800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>442400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>229800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1076100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1568900</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1981600</v>
+      </c>
+      <c r="E27" s="3">
         <v>1831600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2425200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2117000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1156300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1617900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1690500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1259100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>812200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>648100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>312000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>120700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>955200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1437400</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1617,20 +1677,23 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>630700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-636700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>393900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>456200</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E32" s="3">
         <v>27200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>32200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>39900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>69800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-40700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-28600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-190700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1983100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1626400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2059400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1823700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1177200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>578900</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2089000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1932700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2498100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2172600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1201200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1621700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1826300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1415500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>812200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>648100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>942700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-516000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1349000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1893700</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2089000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1932700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2498100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2172600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1201200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1621700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1826300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1415500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>812200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>648100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>942700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-516000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1349000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1893700</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,125 +2072,132 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9892700</v>
+      </c>
+      <c r="E41" s="3">
         <v>12476200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8948700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6351600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9180600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5537100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6061400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6466900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5463200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4465200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4213200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9364800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4853800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5647100</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22818100</v>
+      </c>
+      <c r="E42" s="3">
         <v>18215800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>20372700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>19260200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>22333400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>14518100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>16046500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>21286100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>12152400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10478600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>14255500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>39630600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>47429400</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6099900</v>
+      </c>
+      <c r="E43" s="3">
         <v>8598900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6635000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7736000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6759600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8043900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7755700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6861800</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -2121,9 +2213,12 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2145,12 +2240,12 @@
       <c r="I44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K44" s="3">
         <v>400</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -2166,36 +2261,39 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3417100</v>
+      </c>
+      <c r="E45" s="3">
         <v>3229200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2949300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2520900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2451500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2131900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1820100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1945100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2211,36 +2309,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>51046100</v>
+      </c>
+      <c r="E46" s="3">
         <v>53874000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>57522300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>47485200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>46872600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>39901000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>41740500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>42529600</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2256,144 +2357,156 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>33116700</v>
+        <v>29734600</v>
       </c>
       <c r="E47" s="3">
+        <v>33573300</v>
+      </c>
+      <c r="F47" s="3">
         <v>33811000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>37460700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>34932400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>32351800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>28724300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28818200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>338000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>476500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>525200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1621000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>871900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>816800</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4937200</v>
+      </c>
+      <c r="E48" s="3">
         <v>4983700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4559000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4158200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4046000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2914500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2201200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2319200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2168700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2088800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2315500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5236300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4968600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3197500</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>552200</v>
+      </c>
+      <c r="E49" s="3">
         <v>582000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>506100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>485000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>535900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>536100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>320900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>269700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>372500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>310700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>239500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>489400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>728100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>394100</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>17293300</v>
+        <v>15193100</v>
       </c>
       <c r="E52" s="3">
+        <v>16836600</v>
+      </c>
+      <c r="F52" s="3">
         <v>17375400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11554700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11178600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10625300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8782100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2000500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>235100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>169100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>215400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>77631000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>200600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>70400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>355900000</v>
+      </c>
+      <c r="E54" s="3">
         <v>384037900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>382053600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>375418800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>366711400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>313541700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>305813800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>296084700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>239226000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>215976000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>218827000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>310028000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>274766000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>275257000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,80 +2784,84 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>253583100</v>
+      </c>
+      <c r="E57" s="3">
         <v>283746600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>276784200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>272720500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>271530900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>229266200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>223391800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>219698500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11404000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6198800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6717900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13975600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1000300</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12014400</v>
+      </c>
+      <c r="E58" s="3">
         <v>9863100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10474200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7069700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9567700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2684200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2072300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3162100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2736,89 +2869,95 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>7098200</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>747300</v>
+      </c>
+      <c r="E59" s="3">
         <v>795100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1352700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1201900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1111100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>182100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>167200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>242000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1714900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1487500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2140100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4189100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3097800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>241300</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>269522700</v>
+      </c>
+      <c r="E60" s="3">
         <v>297751000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>291171000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>282730500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>284092800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>232132500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>225675500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>223140500</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2834,99 +2973,108 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>52292900</v>
+      </c>
+      <c r="E61" s="3">
         <v>54929200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>57545700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>58157500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>53326300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>43408600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>40367300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>40014700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>29549800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>28996600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>31952700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>31315500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>44470300</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8428000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4724200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7685200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9505400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3876200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>15528400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>19696100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13447900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>396700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>470400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>639400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1466000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1843300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1119700</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>331601300</v>
+      </c>
+      <c r="E66" s="3">
         <v>358283300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>356904800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>351198600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>342153300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>291460600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>286094000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>276833900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>223528000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>201776000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>204261000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>293819000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>259061000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>259836000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18243700</v>
+      </c>
+      <c r="E72" s="3">
         <v>19268400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18885100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17959400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17705400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16045600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15382600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14621900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11250900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10157300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11473900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>23865100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11660400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10932000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23081300</v>
+      </c>
+      <c r="E76" s="3">
         <v>24420000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22870300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21694800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21183700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18631900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19528300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19064500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15697300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14199500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14566600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16209000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15704600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15421100</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2089000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1932700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2498100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2172600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1201200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1621700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1826300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1415500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>812200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>648100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>942700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-516000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1349000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1893700</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>673200</v>
+      </c>
+      <c r="E83" s="3">
         <v>641800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>609500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>539500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>366500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>326800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>124300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>127300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>194100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>178200</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3">
         <v>273400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>244500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>240800</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6458500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-10452600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3905800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-16816200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-21844000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11725400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4343700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14616200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3777100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-284100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3234100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3633400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-121000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-942600</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-150200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-127000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-137500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-137200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-372100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-106600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-151900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-95800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-129100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-145100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-212100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-204600</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1738300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5541200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8955000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1338300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7438900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9944900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1763300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3253700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>942900</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
         <v>-357600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1975800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2124000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>702000</v>
+      </c>
+      <c r="E96" s="3">
         <v>855600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>593800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>364900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>509500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>518600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>435000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>481500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-129600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-373700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-306500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-344300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-288400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-177300</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3152400</v>
+      </c>
+      <c r="E100" s="3">
         <v>9497700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>20241500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>27625300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>27332800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>18690700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>13934400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>12706400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>256500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-356200</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
         <v>3803800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2248200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>154300</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1112000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-131200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>24500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>890900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-843900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>165800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>210100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-493000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-50400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>201600</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3">
         <v>-86400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-143800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>24700</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2217300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2824400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10819000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2745100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3306500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-307800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-144100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-639400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>729400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>504100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-243600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-273700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-537200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1360500</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/WF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WF_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>WF</t>
   </si>
@@ -656,153 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7762200</v>
+        <v>6901900</v>
       </c>
       <c r="E8" s="3">
+        <v>6751700</v>
+      </c>
+      <c r="F8" s="3">
         <v>7325300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7969300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7398600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6310500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5947900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6157300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5349900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6554500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6436700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7461100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8639000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9148600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9763900</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E9" s="3">
         <v>26700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>30600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>30300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>27200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>26300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>25200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>24800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>24300</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
@@ -818,39 +824,42 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>7735500</v>
+        <v>6876600</v>
       </c>
       <c r="E10" s="3">
+        <v>6725000</v>
+      </c>
+      <c r="F10" s="3">
         <v>7294700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7939000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7371400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6284200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5922800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6132500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5325600</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -866,9 +875,12 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,39 +998,42 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>127700</v>
+      </c>
+      <c r="E14" s="3">
         <v>21700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>40700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>28000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>64100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>152200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>24400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1030,57 +1049,63 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>611900</v>
+      </c>
+      <c r="E15" s="3">
         <v>572100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>542600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>492600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>396800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>208800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>183300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>190900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>184400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-194100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-178200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-184600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-215000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-187500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-177900</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4865500</v>
+        <v>4322900</v>
       </c>
       <c r="E17" s="3">
+        <v>3855000</v>
+      </c>
+      <c r="F17" s="3">
         <v>4599300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4406900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4226800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4389200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3524200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3609800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3334500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3375300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3735900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4725900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6553500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6595600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7124100</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2579000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2896700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2726000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3562400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3171800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1921300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2423700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2547500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2015400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3179200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2700800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2735200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2085400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2553000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2639700</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,104 +1244,111 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-382200</v>
+      </c>
+      <c r="E20" s="3">
         <v>16400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-27200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-32200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-39900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-69800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>40700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>28600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>190700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1983100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1626400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2059400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1823700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1177200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-578900</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3573000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3452300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3295800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4087100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3608500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2199900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2566300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2709800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2009100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1390200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1250200</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>532200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1623200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2301600</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1337,8 +1376,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1355,105 +1394,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2833500</v>
+      </c>
+      <c r="E23" s="3">
         <v>2858600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2712500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3566600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3147600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1838900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2358700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2519500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1824900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1196100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1074400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>675900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>261800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1375900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2060800</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>597600</v>
+      </c>
+      <c r="E24" s="3">
         <v>711700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>686800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>923500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>790700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>446600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>593700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>676600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>392600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>212400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>278600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>233400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>31900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>299700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>491900</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2235900</v>
+      </c>
+      <c r="E26" s="3">
         <v>2146900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2025700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2643100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2356800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1392300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1764900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1842900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1432300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>983700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>795800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>442400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>229800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1076100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1568900</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2060400</v>
+      </c>
+      <c r="E27" s="3">
         <v>1981600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1831600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2425200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2117000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1156300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1617900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1690500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1259100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>812200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>648100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>312000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>120700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>955200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1437400</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1680,20 +1740,23 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>630700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-636700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>393900</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>456200</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>382200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-16400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>27200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>32200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>39900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>69800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-40700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-28600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-190700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1983100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1626400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2059400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1823700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1177200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>578900</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2164400</v>
+      </c>
+      <c r="E33" s="3">
         <v>2089000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1932700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2498100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2172600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1201200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1621700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1826300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1415500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>812200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>648100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>942700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-516000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1349000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1893700</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2164400</v>
+      </c>
+      <c r="E35" s="3">
         <v>2089000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1932700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2498100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2172600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1201200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1621700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1826300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1415500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>812200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>648100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>942700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-516000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1349000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1893700</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,134 +2158,141 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10408300</v>
+      </c>
+      <c r="E41" s="3">
         <v>9892700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12476200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8948700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6351600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9180600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5537100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6061400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6466900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5463200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4465200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4213200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9364800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4853800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5647100</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>30478600</v>
+      </c>
+      <c r="E42" s="3">
         <v>22818100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>18215800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>20372700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>19260200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>22333400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>14518100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>16046500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>21286100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>12152400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>10478600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>14255500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>39630600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>47429400</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7082500</v>
+      </c>
+      <c r="E43" s="3">
         <v>6099900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8598900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6635000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7736000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6759600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8043900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7755700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6861800</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -2216,9 +2308,12 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2243,12 +2338,12 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3">
         <v>400</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -2264,39 +2359,42 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5813900</v>
+      </c>
+      <c r="E45" s="3">
         <v>3417100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3229200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2949300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2520900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2451500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2131900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1820100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1945100</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2312,39 +2410,42 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>70334000</v>
+      </c>
+      <c r="E46" s="3">
         <v>51046100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>53874000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>57522300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>47485200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>46872600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>39901000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>41740500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>42529600</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2360,153 +2461,165 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>29734600</v>
+        <v>51061400</v>
       </c>
       <c r="E47" s="3">
+        <v>29491700</v>
+      </c>
+      <c r="F47" s="3">
         <v>33573300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>33811000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>37460700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>34932400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>32351800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28724300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28818200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>338000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>476500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>525200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1621000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>871900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>816800</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5254900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4937200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4983700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4559000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4158200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4046000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2914500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2201200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2319200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2168700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2088800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2315500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5236300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4968600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3197500</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>503500</v>
+      </c>
+      <c r="E49" s="3">
         <v>552200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>582000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>506100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>485000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>535900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>536100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>320900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>269700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>372500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>310700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>239500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>489400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>728100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>394100</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>15193100</v>
+        <v>22900500</v>
       </c>
       <c r="E52" s="3">
+        <v>15436000</v>
+      </c>
+      <c r="F52" s="3">
         <v>16836600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17375400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11554700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11178600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10625300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8782100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2000500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>235100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>169100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>215400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>77631000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>200600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>70400</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>416660200</v>
+      </c>
+      <c r="E54" s="3">
         <v>355900000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>384037900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>382053600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>375418800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>366711400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>313541700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>305813800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>296084700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>239226000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>215976000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>218827000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>310028000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>274766000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>275257000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,86 +2914,90 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>266776300</v>
+      </c>
+      <c r="E57" s="3">
         <v>253583100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>283746600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>276784200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>272720500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>271530900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>229266200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>223391800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>219698500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11404000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6198800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6717900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13975600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1000300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11198400</v>
+      </c>
+      <c r="E58" s="3">
         <v>12014400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9863100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10474200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7069700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9567700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2684200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2072300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3162100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -2872,95 +3005,101 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>7098200</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1226800</v>
+      </c>
+      <c r="E59" s="3">
         <v>747300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>795100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1352700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1201900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1111100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>182100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>167200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>242000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1714900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1487500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2140100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4189100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3097800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>241300</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>282288500</v>
+      </c>
+      <c r="E60" s="3">
         <v>269522700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>297751000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>291171000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>282730500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>284092800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>232132500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>225675500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>223140500</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2976,105 +3115,114 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>61015700</v>
+      </c>
+      <c r="E61" s="3">
         <v>52292900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>54929200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>57545700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>58157500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>53326300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>43408600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>40367300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>40014700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>29549800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>28996600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>31952700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>31315500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>44470300</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>46041700</v>
+      </c>
+      <c r="E62" s="3">
         <v>8428000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4724200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7685200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9505400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3876200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15528400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>19696100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13447900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>396700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>470400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>639400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1466000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1843300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1119700</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>390433100</v>
+      </c>
+      <c r="E66" s="3">
         <v>331601300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>358283300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>356904800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>351198600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>342153300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>291460600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>286094000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>276833900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>223528000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>201776000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>204261000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>293819000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>259061000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>259836000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19944300</v>
+      </c>
+      <c r="E72" s="3">
         <v>18243700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19268400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18885100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17959400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>17705400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16045600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15382600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14621900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11250900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>10157300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11473900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>23865100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11660400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10932000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24951000</v>
+      </c>
+      <c r="E76" s="3">
         <v>23081300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24420000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22870300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21694800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21183700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18631900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19528300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19064500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15697300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14199500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14566600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16209000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15704600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15421100</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2164400</v>
+      </c>
+      <c r="E81" s="3">
         <v>2089000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1932700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2498100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2172600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1201200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1621700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1826300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1415500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>812200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>648100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>942700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-516000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1349000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1893700</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>733500</v>
+      </c>
+      <c r="E83" s="3">
         <v>673200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>641800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>609500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>539500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>366500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>326800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>124300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>127300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>194100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>178200</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>273400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>244500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>240800</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-136800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6458500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-10452600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3905800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-16816200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-21844000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11725400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4343700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14616200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3777100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-284100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3234100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3633400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-121000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-942600</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-225800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-150200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-127000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-137500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-137200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-372100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-106600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-151900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-95800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-129100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-145100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-212100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-204600</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6844800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1738300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5541200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8955000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1338300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7438900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9944900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1763300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3253700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>942900</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-357600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1975800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2124000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>746300</v>
+      </c>
+      <c r="E96" s="3">
         <v>702000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>855600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>593800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>364900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>509500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>518600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>435000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>481500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-129600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-373700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-306500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-344300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-288400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-177300</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>14911600</v>
+      </c>
+      <c r="E100" s="3">
         <v>3152400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9497700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>20241500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>27625300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>27332800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>18690700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>13934400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>12706400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>256500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-356200</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>3803800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2248200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>154300</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-158300</v>
+      </c>
+      <c r="E101" s="3">
         <v>1112000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-131200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>24500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>890900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-843900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>165800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>210100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-493000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-50400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>201600</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>-86400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-143800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>24700</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7771700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2217300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2824400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10819000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2745100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3306500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-307800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-144100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-639400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>729400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>504100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-243600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-273700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-537200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1360500</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/WF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WF_YR_FIN.xlsx
@@ -1008,7 +1008,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>127700</v>
+        <v>-274800</v>
       </c>
       <c r="E14" s="3">
         <v>21700</v>
@@ -1251,7 +1251,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-382200</v>
+        <v>20300</v>
       </c>
       <c r="E20" s="3">
         <v>16400</v>
@@ -1302,7 +1302,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3573000</v>
+        <v>3170500</v>
       </c>
       <c r="E21" s="3">
         <v>3452300</v>
@@ -1863,7 +1863,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>382200</v>
+        <v>-20300</v>
       </c>
       <c r="E32" s="3">
         <v>-16400</v>
